--- a/ai_logs/VoXuanLong_Ai_Log.xlsx
+++ b/ai_logs/VoXuanLong_Ai_Log.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DD31205-F928-4DCC-BC6E-8C99AB35953D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{74262D9E-EBB9-4520-817E-B01475A65BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="158">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -326,6 +326,9 @@
   </si>
   <si>
     <t>Sơ đồ Draw.io sau khi cập nhật mũi tên --&gt; hướng từ Booking sang Invoice.</t>
+  </si>
+  <si>
+    <t>vdcvbbn</t>
   </si>
   <si>
     <t>-</t>
@@ -711,22 +714,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -752,6 +739,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1066,14 +1069,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
@@ -1305,28 +1308,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A3" s="6" t="s">
@@ -1439,7 +1442,7 @@
       <c r="B7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="18" t="s">
         <v>43</v>
       </c>
       <c r="D7" s="7" t="s">
@@ -1451,10 +1454,10 @@
       <c r="F7" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="G7" s="27" t="s">
+      <c r="G7" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="H7" s="30" t="s">
+      <c r="H7" s="24" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1477,10 +1480,10 @@
       <c r="F8" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="31" t="s">
+      <c r="G8" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="H8" s="32" t="s">
+      <c r="H8" s="26" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1503,10 +1506,10 @@
       <c r="F9" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="G9" s="33" t="s">
+      <c r="G9" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="H9" s="31" t="s">
+      <c r="H9" s="25" t="s">
         <v>91</v>
       </c>
     </row>
@@ -1514,11 +1517,13 @@
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+      <c r="D10" s="7" t="s">
+        <v>92</v>
+      </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="28"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="22"/>
     </row>
     <row r="11" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A11" s="7"/>
@@ -1527,7 +1532,7 @@
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
-      <c r="H11" s="29"/>
+      <c r="H11" s="23"/>
     </row>
     <row r="12" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A12" s="7"/>
@@ -1545,7 +1550,7 @@
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
-      <c r="G13" s="25"/>
+      <c r="G13" s="19"/>
       <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:8" ht="80.099999999999994" customHeight="1">
@@ -1573,8 +1578,8 @@
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="26" t="s">
-        <v>92</v>
+      <c r="G16" s="20" t="s">
+        <v>93</v>
       </c>
       <c r="H16" s="7"/>
     </row>
@@ -1697,43 +1702,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="A1" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
+      <c r="A2" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
     </row>
     <row r="3" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1">
@@ -1741,19 +1746,19 @@
         <v>69</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1920,73 +1925,73 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -2010,202 +2015,202 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
+      <c r="A1" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="A2" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>134</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>133</v>
       </c>
       <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D10" s="13"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D14" s="13"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>134</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>133</v>
       </c>
       <c r="D15" s="13"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D17" s="13"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D18" s="13"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2213,13 +2218,13 @@
         <v>47</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:4">

--- a/ai_logs/VoXuanLong_Ai_Log.xlsx
+++ b/ai_logs/VoXuanLong_Ai_Log.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{74262D9E-EBB9-4520-817E-B01475A65BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{72BF2A17-1D72-4392-83B1-449CD29D2E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="180">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -328,7 +328,57 @@
     <t>Sơ đồ Draw.io sau khi cập nhật mũi tên --&gt; hướng từ Booking sang Invoice.</t>
   </si>
   <si>
-    <t>vdcvbbn</t>
+    <t>Phân rã cấu trúc hệ thống quản lý đặt chỗ/dịch vụ phức tạp thành các khối lớp (classes) thực thể có thể quản lý và lập trình được bằng Java.</t>
+  </si>
+  <si>
+    <t>classDiagram %% --- KHỐI QUẢN LÝ TÀI KHOẢN &amp; NGƯỜI DÙNG --- class User... class Customer... class Staff... class Admin... định nghĩa mối quan hệ không gian" (Đây chính là cấu trúc code ban đầu bạn đưa cho AI xử lý).</t>
+  </si>
+  <si>
+    <t>AI phân tích và đề xuất phân chia hệ thống thành 5 khối nghiệp vụ chính: Khối quản lý tài khoản, Khối quản lý phòng/dịch vụ, Khối đặt chỗ, Khối hóa đơn/thanh toán, và Khối báo cáo/feedback.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Nhận thấy nếu gộp tất cả các chức năng vào một vài class lớn sẽ vi phạm nguyên tắc Đơn nhiệm (Single Responsibility Principle) trong lập trình OOP Java, gây khó khăn khi viết code hàm main và phân chia công việc trong nhóm.
+Contextualization: Trong bối cảnh LAB211, hệ thống cần được module hóa rõ ràng để dễ dàng xây dựng các lớp xử lý danh sách (ArrayList) tương ứng cho từng thực thể.
+Creative Synthesis: Thực hiện tách biệt hoàn toàn thông tin người dùng cơ bản (User) ra khỏi các vai trò chuyên biệt (Customer, Staff, Admin) và tách đơn đặt phòng tổng quan (Booking) ra khỏi các dòng dịch vụ/phòng cụ thể (BookingDetail).
+Decision: Quyết định cấu trúc hệ thống thành mô hình 13 lớp độc lập và nhóm thành 5 phân hệ logic rõ ràng như sơ đồ thiết kế để tiến hành phân chia nhiệm vụ viết code.</t>
+  </si>
+  <si>
+    <t>File sơ đồ cấu trúc các Class ban đầu trong tài liệu báo cáo.</t>
+  </si>
+  <si>
+    <t>Thiết kế thuật toán tính toán số tiền chi tiết cho từng hạng mục đặt phòng/dịch vụ trong hóa đơn tổng.</t>
+  </si>
+  <si>
+    <t>Thiết kế logic xử lý cho hàm calculateSubTotal() trong BookingDetail và generateInvoice() trong Invoice.</t>
+  </si>
+  <si>
+    <t>AI đề xuất thuật toán tính: subTotal = quantity * price cho từng dòng và duyệt vòng lặp qua danh sách để tính tổng tiền hóa đơn: finalAmount = sum(subTotal) + tax - discount.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Phát hiện đề xuất của AI quá đơn giản vì chưa tính tới thời gian lưu trú (số đêm ở phòng) mà chỉ nhân số lượng đơn thuần.
+Contextualization: Logic nghiệp vụ đặt phòng khách sạn yêu cầu giá phòng phải bằng đơn giá * số đêm (được tính từ khoảng cách giữa checkInDate và checkOutDate), còn dịch vụ phụ trợ mới bằng đơn giá * số lượng.
+Creative Synthesis: Sửa lại thuật toán: Sử dụng các thư viện xử lý ngày tháng của Java (java.time.LocalDate và ChronoUnit.DAYS.between) để tính số đêm thực tế, sau đó viết hàm kiểm tra loại mặt hàng (Room hay Service) để áp dụng công thức tính tiền chuẩn xác.
+Decision: Cài đặt thuật toán tính toán động dựa trên khoảng cách ngày tháng để đảm bảo hóa đơn xuất ra chính xác tuyệt đối, không làm thất thoát doanh thu.</t>
+  </si>
+  <si>
+    <t>Cấu trúc thuộc tính checkInDate, checkOutDate và hàm calculateSubTotal() trên sơ đồ.</t>
+  </si>
+  <si>
+    <t>Lựa chọn cấu trúc dữ liệu phù hợp trong Java để triển khai mối quan hệ giữa Invoice và Payment (Invoice 1 *-- 1..* Payment).</t>
+  </si>
+  <si>
+    <t>Tư vấn cấu trúc lưu trữ lịch sử các đợt thanh toán của một hóa đơn cụ thể.</t>
+  </si>
+  <si>
+    <t>AI đề xuất tạo một mảng cố định (Payment[]) hoặc dùng một quan hệ độc lập để truy vấn cơ sở dữ liệu.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Việc dùng mảng cố định Payment[] sẽ bị giới hạn số lần thanh toán của khách hàng (ví dụ khách muốn trả góp hoặc chia làm nhiều đợt thanh toán nhỏ), gây cứng nhắc cho code Java.
+Contextualization: Đồ án LAB211 yêu cầu tính linh hoạt cao và tối ưu hóa việc quản lý bộ nhớ động khi chạy chương trình trên Console.
+Creative Synthesis &amp; Decision: Nhận diện mẫu (Pattern) mối quan hệ 1-nhiều mạnh (Composition). Quyết định sử dụng ArrayList&lt;Payment&gt; đặt trực tiếp làm một thuộc tính ẩn (private) bên trong lớp Invoice. Điều này đảm bảo khi một đối tượng Invoice được khởi tạo, nó có thể tự quản lý danh sách các đợt thanh toán của chính nó một cách linh hoạt và khi hóa đơn bị hủy, danh sách thanh toán cũng tự động được giải phóng khỏi bộ nhớ RAM.</t>
+  </si>
+  <si>
+    <t>Ký hiệu hình thoi đặc (*--) kết nối giữa lớp Invoice và Payment trên Draw.io.</t>
   </si>
   <si>
     <t>-</t>
@@ -373,6 +423,36 @@
     <t>Used real paper 'Jones et al. 2022'</t>
   </si>
   <si>
+    <t>Logic Error</t>
+  </si>
+  <si>
+    <t>AI tạo sơ đồ lớp tự động với tất cả các thuộc tính dữ liệu đều để dấu cộng (+) – tức là phạm vi truy cập Public.</t>
+  </si>
+  <si>
+    <t>Trong thiết kế hướng đối tượng (OOP) bằng Java, việc để thuộc tính thực thể là Public là lỗi thiết kế nghiêm trọng, phá vỡ tính đóng gói (Encapsulation). Thuộc tính bắt buộc phải là Private (-).</t>
+  </si>
+  <si>
+    <t>Tôi tự kiểm tra, đối chiếu sơ đồ AI sinh ra với kiến thức nền tảng về tính đóng gói đã học trong bộ môn Java OOP và phát hiện điểm bất hợp lý.</t>
+  </si>
+  <si>
+    <t>Tôi đã chất vấn và yêu cầu AI sửa lại mã nguồn sơ đồ thành dấu trừ (-) đối với toàn bộ thuộc tính dữ liệu, đảm bảo sơ đồ chuẩn hóa 100% trước khi đem báo cáo.</t>
+  </si>
+  <si>
+    <t>Oversimplification</t>
+  </si>
+  <si>
+    <t>AI đề xuất thuật toán tính tiền trong hàm calculateSubTotal() bằng công thức đơn giản: Tổng tiền = Số lượng * Đơn giá</t>
+  </si>
+  <si>
+    <t>Đối với nghiệp vụ đặt phòng khách sạn/vé, giá phòng phải phụ thuộc vào thời gian lưu trú (Số đêm phòng = checkOutDate - checkInDate), công thức của AI sẽ làm tính toán sai hoàn toàn doanh thu thực tế.</t>
+  </si>
+  <si>
+    <t>Tôi rà soát lại các thuộc tính ngày tháng (checkInDate, checkOutDate) trong lớp Booking và đối chiếu với logic vận hành thực tế của một hệ thống đặt phòng.</t>
+  </si>
+  <si>
+    <t>Tôi đã loại bỏ công thức đơn giản của AI và tự thiết kế lại thuật toán tính toán bằng cách tích hợp thư viện xử lý thời gian của Java để tính toán số đêm thực tế cho thực thể Phòng.</t>
+  </si>
+  <si>
     <t>HALLUCINATION TYPES REFERENCE:</t>
   </si>
   <si>
@@ -391,16 +471,10 @@
     <t>Fake papers, fake APIs, fake data</t>
   </si>
   <si>
-    <t>Oversimplification</t>
-  </si>
-  <si>
     <t>AI bỏ qua edge cases, exceptions</t>
   </si>
   <si>
     <t>Code không handle array rỗng</t>
-  </si>
-  <si>
-    <t>Logic Error</t>
   </si>
   <si>
     <t>AI đưa kết luận sai về 'best practice'</t>
@@ -677,7 +751,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -722,12 +796,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -755,6 +823,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1069,14 +1140,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
@@ -1308,28 +1379,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="3" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A3" s="6" t="s">
@@ -1457,7 +1528,7 @@
       <c r="G7" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="H7" s="24" t="s">
+      <c r="H7" s="22" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1480,10 +1551,10 @@
       <c r="F8" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="H8" s="26" t="s">
+      <c r="H8" s="24" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1506,42 +1577,90 @@
       <c r="F9" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="G9" s="27" t="s">
+      <c r="G9" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="H9" s="25" t="s">
+      <c r="H9" s="23" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
+      <c r="A10" s="7">
+        <v>7</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="D10" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="22"/>
+      <c r="E10" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G10" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="H11" s="23"/>
+      <c r="A11" s="7">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="H12" s="7"/>
+      <c r="A12" s="7">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A13" s="7"/>
@@ -1579,7 +1698,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="20" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="H16" s="7"/>
     </row>
@@ -1702,43 +1821,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
+      <c r="A1" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
+      <c r="A2" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
     </row>
     <row r="3" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1">
@@ -1746,38 +1865,60 @@
         <v>69</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="91.5">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="A6" s="7">
+        <v>8</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1">
       <c r="A7" s="7"/>
@@ -1925,73 +2066,73 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="10" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="7" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="7" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="7" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="7" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -2015,202 +2156,202 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
+      <c r="A1" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="33" t="s">
-        <v>126</v>
-      </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
+      <c r="A2" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="12" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="12" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="12" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="12" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="D10" s="13"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="6" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="12" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="D14" s="13"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="D15" s="13"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="12" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="12" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="D17" s="13"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="12" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="D18" s="13"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="14" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="15" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="15" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="16" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2218,13 +2359,13 @@
         <v>47</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:4">

--- a/ai_logs/VoXuanLong_Ai_Log.xlsx
+++ b/ai_logs/VoXuanLong_Ai_Log.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72BF2A17-1D72-4392-83B1-449CD29D2E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FCE5DE6-64E4-4F7C-8D1B-807FB682329F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="217">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -381,7 +381,90 @@
     <t>Ký hiệu hình thoi đặc (*--) kết nối giữa lớp Invoice và Payment trên Draw.io.</t>
   </si>
   <si>
-    <t>-</t>
+    <t>Thiết kế Access Modifier (Phạm vi truy cập) cho các thuộc tính trong lớp Seat và Section để đảm bảo đúng nguyên lý lập trình hướng đối tượng Java.</t>
+  </si>
+  <si>
+    <t>"Tại sao các thuộc tính trong class Seat và Section sinh ra lại để hết là dấu cộng (+) public thế này? Có giữ nguyên public được không?"</t>
+  </si>
+  <si>
+    <t>AI giải thích việc để public giúp các tầng khác truy cập trực tiếp vào biến dữ liệu nhanh hơn mà không bị tốn bộ nhớ đệm, khuyên nên giữ nguyên cấu trúc tự động này.</t>
+  </si>
+  <si>
+    <t>* Critical Thinking: Nhận thấy việc để toàn bộ thuộc tính (seatId, seatNumber, isAvailable) là public vi phạm nghiêm trọng nguyên lý Đóng gói (Encapsulation) của OOP Java. Trong thực thể (Entity), các thuộc tính bắt buộc phải để private (-) và chỉ tương tác thông qua các hàm Getter/Setter để bảo vệ an toàn dữ liệu.
+Contextualization: Giảng viên chấm môn LAB chấm rất gắt tính đóng gói; để thuộc tính lộ ra ngoài sẽ bị trừ điểm nặng ở tầng Model.
+Decision: Phớt lờ lời khuyên của AI, chủ động sửa tất cả thuộc tính thành private và tự viết thêm Constructor đầy đủ tham số cùng các cặp hàm Getter/Setter.</t>
+  </si>
+  <si>
+    <t>Git Diff</t>
+  </si>
+  <si>
+    <t>Thiết kế thuật toán ánh xạ (map) dữ liệu tối ưu trên RAM ở tầng Repository để liên kết file seats.csv lộn xộn với file section.csv lộn xộn khi đọc file vào hệ thống.</t>
+  </si>
+  <si>
+    <t>"Làm sao để map dữ liệu giữa file seats.csv lộn xộn và file section.csv lộn xộn một cách tối ưu khi load chương trình lên?"</t>
+  </si>
+  <si>
+    <t>AI đề xuất giải pháp dùng vòng lặp for lồng nhau (Nested Loop) để quét liên tục qua cả 2 danh sách trên RAM nhằm tìm ra các cặp ID trùng nhau.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Phát hiện ra thuật toán vòng lặp lồng nhau của AI quá thô sơ và kém hiệu năng với độ phức tạp $O(N \times M)$. Khi quy mô dữ liệu tăng lên $\ge$ 10,000 dòng, thuật toán này sẽ làm nghẽn mạch hệ thống và chắc chắn thất bại trước tiêu chuẩn thời gian phản hồi dưới 500ms của đề bài.Contextualization: Tiêu chuẩn hiệu năng của bài Lab bắt buộc tốc độ xử lý dữ liệu trên RAM phải đạt mức tối ưu cao nhất.Decision: Loại bỏ thuật toán của AI. Tự cấu trúc lại logic bằng cách nạp file Khu vực vào một cấu trúc HashMap&lt;Integer, Section&gt; trước. Khi duyệt qua file Ghế, chỉ cần dùng hàm .get(sectionRef) với độ phức tạp lý tưởng $O(1)$, đưa tốc độ xử lý thực tế xuống dưới 140ms.</t>
+  </si>
+  <si>
+    <t>Ảnh chụp màn hình Code</t>
+  </si>
+  <si>
+    <t>Data Evaluation</t>
+  </si>
+  <si>
+    <t>Lựa chọn kiểu dữ liệu tối ưu cho các trường khóa chính và khóa ngoại (seatId và sectionRef) bên trong lớp thực thể Seat.java.</t>
+  </si>
+  <si>
+    <t>"Thầy giáo bảo phải đổi ID sang kiểu số nguyên int, nhưng AI lại thiết kế kiểu String, giờ sửa lại thế nào cho chuẩn?"</t>
+  </si>
+  <si>
+    <t>AI khuyên nên giữ nguyên kiểu dữ liệu String vì chuỗi văn bản sẽ dễ đọc trực tiếp từ file CSV hơn và không phải viết thêm mã ép kiểu phức tạp.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Nhận ra thiết kế của AI rất thiếu tối ưu. Sử dụng kiểu String cho các trường ID bản chất là số nguyên sẽ gây lãng phí dung lượng bộ nhớ RAM một cách vô ích khi nhân lên với 10,000 dòng dữ liệu. Ngoài ra, việc so sánh hai chuỗi bằng hàm .equals() luôn chậm hơn nhiều so với so sánh hai số nguyên bằng toán tử ==.
+Contextualization: Nguyên lý định kiểu dữ liệu nghiêm ngặt (Strong Typing) là bắt buộc để tối ưu kiến trúc Java sạch.
+Decision: Bác bỏ đề xuất của AI. Refactor lại toàn bộ kiểu dữ liệu của ID thành kiểu số nguyên int, đồng thời tự viết thêm mã xử lý ép kiểu Integer.parseInt() trong luồng đọc file CSV.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tối ưu hóa hiệu năng lưu trữ file khi ghi một tập dữ liệu lớn ($\ge$ 10,000 dòng) từ bộ nhớ RAM xuống file cứng seats.csv.</t>
+  </si>
+  <si>
+    <t>"Hàm ghi file của tôi chạy mất hơn 1 giây, thầy bảo thế là quá chậm, có cách nào tối ưu code Java không?"</t>
+  </si>
+  <si>
+    <t>AI cung cấp đoạn code mẫu sử dụng thư viện FileWriter thông thường và giải thích rằng thời gian chạy chậm là do tốc độ đọc ghi phần cứng của ổ đĩa/SSD máy tính.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Phát hiện đây là lỗi ảo tưởng đổ lỗi cho phần cứng (Oversimplification). Thư viện FileWriter ghi trực tiếp từng ký tự xuống đĩa vật lý, tạo ra hàng ngàn tác vụ chặn dòng I/O gây tốn thời gian. Lỗi hoàn toàn nằm ở thuật toán chọn thư viện code chứ không phải phần cứng.
+Contextualization: Yêu cầu bắt buộc của bài Lab là thời gian ghi file lớn phải nằm dưới ngưỡng 500ms.
+Decision: Thay thế hoàn toàn FileWriter bằng lớp BufferedWriter. Thư viện này giúp gom toàn bộ dữ liệu 10,000 dòng vào bộ đệm RAM rồi đổ xuống ổ đĩa đúng 1 lần duy nhất, tăng tốc độ xử lý vượt bậc và giảm thời gian xuống còn ~100ms.</t>
+  </si>
+  <si>
+    <t>Báo cáo số liệu hiệu năng (Metrics Log)</t>
+  </si>
+  <si>
+    <t>System Robustness</t>
+  </si>
+  <si>
+    <t>Triển khai cơ chế bắt lỗi ngoại lệ (Exception Handling) để xử lý các tình huống file CSV đầu vào xuất hiện dòng trống hoặc dữ liệu bị lỗi định dạng.</t>
+  </si>
+  <si>
+    <t>"Nếu file seats.csv tự dưng có 1 dòng trống ở giữa thì chương trình bị crash lỗi NumberFormatException lập tức, xử lý thế nào?"</t>
+  </si>
+  <si>
+    <t>AI khẳng định các file dữ liệu mẫu dùng để kiểm thử sẽ không bao giờ chứa dòng trống, vì vậy việc viết thêm code phòng thủ cho trường hợp này là không cần thiết.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Bắt bài giả định chủ quan và thiếu thực tế của AI. Trong các hệ thống chạy thực tế, file dữ liệu rất dễ có dòng trống ở cuối file hoặc ký tự lạ do người dùng vô tình nhập vào. Việc thiếu Try-Catch bắt lỗi ép kiểu dữ liệu sẽ khiến ứng dụng sập nguồn (Crash) ngay lập tức.
+Contextualization: Tiêu chuẩn chấm mã nguồn Java yêu cầu hệ thống phải có tính bền vững (Robustness) cao trước dữ liệu bẩn đầu vào.
+Decision: Chủ động chèn thêm câu lệnh kiểm tra điều kiện dữ liệu rỗng if (line.trim().isEmpty()) continue; để bỏ qua dòng trống, đồng thời bọc toàn bộ khối lệnh parse chuỗi vào trong khối try-catch để hệ thống vận hành liên tục ổn định.</t>
+  </si>
+  <si>
+    <t>Ảnh chụp màn hình Log lỗi ngoại lệ</t>
   </si>
   <si>
     <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
@@ -451,6 +534,42 @@
   </si>
   <si>
     <t>Tôi đã loại bỏ công thức đơn giản của AI và tự thiết kế lại thuật toán tính toán bằng cách tích hợp thư viện xử lý thời gian của Java để tính toán số đêm thực tế cho thực thể Phòng.</t>
+  </si>
+  <si>
+    <t>AI sinh mã nguồn tự động cho hai lớp thực thể Seat và Section với toàn bộ thuộc tính đều mang phạm vi truy cập Public (+).</t>
+  </si>
+  <si>
+    <t>Trong lập trình hướng đối tượng (OOP) Java, các thuộc tính của lớp thực thể bắt buộc phải khai báo là Private (-) để bảo mật dữ liệu, chống truy cập trực tiếp và phá vỡ tính đóng gói (Encapsulation).</t>
+  </si>
+  <si>
+    <t>Tôi tự đối chiếu mã nguồn do AI sinh ra với quy chuẩn thiết kế lớp (Class Diagram) và kiến thức nền tảng đã học trong bộ môn Java OOP.</t>
+  </si>
+  <si>
+    <t>Tôi đã chất vấn lại AI, yêu cầu chuyển đổi tất cả thuộc tính thành private và bọc lại bằng các cặp hàm Getter/Setter chuẩn chỉnh.</t>
+  </si>
+  <si>
+    <t>AI đề xuất thuật toán dùng vòng lặp for lồng nhau (Nested Loop) để khớp nối mã sectionRef của file ghế với sectionId của file khu vực khi nạp vào RAM.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Thuật toán vòng lặp lồng nhau có độ phức tạp quá cao ($O(N \times M)$). Khi quy mô dữ liệu đẩy lên $\ge$ 10,000 dòng, hệ thống chắc chắn sẽ bị nghẽn và không đạt tiêu chuẩn tốc độ xử lý nhanh dưới 500ms của đề bài.</t>
+  </si>
+  <si>
+    <t>Tôi rà soát lại độ phức tạp thuật toán và phân tích hiệu năng xử lý lý thuyết đối với các tập dữ liệu lớn.</t>
+  </si>
+  <si>
+    <t>Tôi bác bỏ giải thuật thô sơ này, tự mình thiết kế cấu trúc dữ liệu HashMap trên RAM để tối ưu hóa việc tra cứu ánh xạ về độ phức tạp $O(1)$.</t>
+  </si>
+  <si>
+    <t>AI cung cấp mã nguồn sử dụng FileWriter thông thường để ghi dữ liệu lớn và giải thích rằng thời gian chạy chậm (hơn 1 giây) là do cấu hình phần cứng ổ đĩa của máy tính.</t>
+  </si>
+  <si>
+    <t>Nguyên nhân chậm là do code của AI tạo ra quá nhiều tác vụ ghi đĩa liên tục (I/O blocking). Giải pháp chuẩn cho bài toán ghi dữ liệu hàng loạt bắt buộc phải dùng bộ đệm (Buffer).</t>
+  </si>
+  <si>
+    <t>Tôi sử dụng hàm System.currentTimeMillis() trong Java để đo đạc chính xác thời gian chạy thực tế và thấy kết quả bị vượt ngưỡng cho phép rất nhiều.</t>
+  </si>
+  <si>
+    <t>Tôi chủ động thay thế FileWriter bằng BufferedWriter để gom toàn bộ dữ liệu ghi 1 lần duy nhất, đẩy tốc độ xử lý tăng vọt và hạ thời gian xuống còn ~100ms.</t>
   </si>
   <si>
     <t>HALLUCINATION TYPES REFERENCE:</t>
@@ -751,7 +870,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -791,8 +910,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -808,23 +925,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1143,11 +1269,11 @@
       <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
@@ -1382,25 +1508,25 @@
       <c r="A1" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A3" s="6" t="s">
@@ -1525,10 +1651,10 @@
       <c r="F7" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="H7" s="22" t="s">
+      <c r="H7" s="20" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1551,10 +1677,10 @@
       <c r="F8" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="23" t="s">
+      <c r="G8" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="22" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1577,10 +1703,10 @@
       <c r="F9" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="H9" s="23" t="s">
+      <c r="H9" s="21" t="s">
         <v>91</v>
       </c>
     </row>
@@ -1603,10 +1729,10 @@
       <c r="F10" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G10" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="H10" s="24" t="s">
+      <c r="H10" s="22" t="s">
         <v>96</v>
       </c>
     </row>
@@ -1629,10 +1755,10 @@
       <c r="F11" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="H11" s="25" t="s">
+      <c r="H11" s="23" t="s">
         <v>101</v>
       </c>
     </row>
@@ -1655,7 +1781,7 @@
       <c r="F12" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="23" t="s">
         <v>105</v>
       </c>
       <c r="H12" s="7" t="s">
@@ -1663,53 +1789,134 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="7"/>
+      <c r="A13" s="7">
+        <v>10</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G13" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="H14" s="7"/>
+      <c r="A14" s="7">
+        <v>11</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="H15" s="7"/>
+      <c r="A15" s="7">
+        <v>12</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="16" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="H16" s="7"/>
+      <c r="A16" s="7">
+        <v>13</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="G16" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="17" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="H17" s="7"/>
+      <c r="A17" s="7">
+        <v>14</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="H17" s="32" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A18" s="7"/>
@@ -1821,43 +2028,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
+      <c r="A1" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
+      <c r="A2" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
     </row>
     <row r="3" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1">
@@ -1865,19 +2072,19 @@
         <v>69</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="91.5">
@@ -1885,19 +2092,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1">
@@ -1905,44 +2112,80 @@
         <v>8</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
+      <c r="A7" s="7">
+        <v>10</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="A8" s="7">
+        <v>11</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="60" customHeight="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+      <c r="A9" s="7">
+        <v>13</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="60" customHeight="1">
       <c r="A10" s="7"/>
@@ -2066,73 +2309,73 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="10" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>134</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="7" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="7" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>140</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="7" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>143</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="7" t="s">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>145</v>
+        <v>182</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>146</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -2157,201 +2400,201 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="28" t="s">
-        <v>147</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
+        <v>184</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
+      <c r="A2" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>149</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>151</v>
+        <v>188</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>153</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="12" t="s">
-        <v>154</v>
+        <v>191</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="12" t="s">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="12" t="s">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="12" t="s">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>162</v>
+        <v>199</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
-        <v>163</v>
+        <v>200</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>164</v>
+        <v>201</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="D10" s="13"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>165</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="6" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>151</v>
+        <v>188</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>166</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="12" t="s">
-        <v>154</v>
+        <v>191</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>167</v>
+        <v>204</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="D14" s="13"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>168</v>
+        <v>205</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="D15" s="13"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="12" t="s">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>169</v>
+        <v>206</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="12" t="s">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>170</v>
+        <v>207</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="D17" s="13"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="12" t="s">
-        <v>163</v>
+        <v>200</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>171</v>
+        <v>208</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="D18" s="13"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="14" t="s">
-        <v>172</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="15" t="s">
-        <v>173</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="15" t="s">
-        <v>174</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="16" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2359,13 +2602,13 @@
         <v>47</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>179</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28" spans="1:4">

--- a/ai_logs/VoXuanLong_Ai_Log.xlsx
+++ b/ai_logs/VoXuanLong_Ai_Log.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FCE5DE6-64E4-4F7C-8D1B-807FB682329F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NHOM_04_LAB211_TicketBooking\ai_logs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EEB6DEB-FC08-48AA-90C3-211A1E0F1CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -25,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="231">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -717,6 +720,48 @@
   </si>
   <si>
     <t>Tôi có evidence?</t>
+  </si>
+  <si>
+    <t>Xây dựng tính năng tìm kiếm một chiếc ghế cụ thể theo mã ID (seatId) một cách tối ưu ở tầng Service/Repository khi dữ liệu lớn đã được nạp lên RAM.</t>
+  </si>
+  <si>
+    <t>"Hãy viết cho tôi hàm tìm kiếm một chiếc ghế theo ID từ danh sách 5000 ghế trên RAM."</t>
+  </si>
+  <si>
+    <t>AI cung cấp một hàm sử dụng vòng lặp duyệt tuần tự (Linear Search) chạy từ đầu đến cuối danh sách List để so sánh ID từng ghế.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Phát hiện duyệt tuần tự bằng vòng lặp qua một ArrayList cực kỳ kém tối ưu đối với các thao tác tìm kiếm được gọi lặp đi lặp lại nhiều lần, có độ phức tạp thuật toán là $O(N)$. Nếu hệ thống có nhiều lượt truy cập tra cứu ghế cùng lúc sẽ bị trễ.Contextualization: Đồ án rạp phim đòi hỏi thao tác khách hàng click chọn ghế hoặc tra cứu thông tin trạng thái ghế phải phản hồi ngay lập tức.Creative Synthesis: Chuyển đổi cấu trúc lưu trữ từ dạng danh sách phẳng sang cấu trúc ánh xạ để tận dụng cơ chế băm dữ liệu.Decision: Tự tối ưu lại bằng cách lưu trữ danh sách ghế vào một cấu trúc HashMap&lt;Integer, Seat&gt; ngay khi đọc file CSV lên RAM. Khi cần tìm kiếm, chỉ cần gọi hàm map.get(id) đạt độ phức tạp tuyệt đối $O(1)$ - tra cứu tức thì không độ trễ.</t>
+  </si>
+  <si>
+    <t>Ảnh chụp màn hình Code hàm tìm kiếm tối ưu</t>
+  </si>
+  <si>
+    <t>Thực hiện sắp xếp (Sort) lại danh sách ghế đang bị lộn xộn theo thứ tự tăng dần của mã ID trước khi hiển thị lên giao diện Terminal hoặc xuất báo cáo.</t>
+  </si>
+  <si>
+    <t>"Làm sao để sắp xếp danh sách ghế lộn xộn trong List theo thứ tự ID tăng dần?"</t>
+  </si>
+  <si>
+    <t>AI tự viết một đoạn code thủ công dài dòng sử dụng thuật toán sắp xếp nổi bọt (Bubble Sort) với 2 vòng lặp lồng nhau để hoán đổi vị trí các phần tử ghế.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Nhận ra AI đang mắc lỗi đơn giản hóa quá mức (Oversimplification). Thuật toán Bubble Sort có hiệu năng rất tệ $O(N^2)$, hoàn toàn lỗi thời và lãng phí tài nguyên CPU khi xử lý tập dữ liệu lớn, trong khi Java đã tích hợp sẵn các bộ thư viện cực mạnh.Contextualization: Yêu cầu mã nguồn đồ án phải đạt tiêu chuẩn chuyên nghiệp, tinh gọn và tận dụng tối đa sức mạnh API sẵn có của Java Collection Framework.Creative Synthesis: Sử dụng bộ so sánh Comparator kết hợp với biểu thức Lambda để thay thế hoàn toàn các vòng lặp hoán đổi vị trí thủ công.Decision: Bác bỏ hoàn toàn đoạn code sắp xếp thủ công của AI. Thay thế bằng giải pháp chuẩn công nghiệp: sử dụng phương thức Collections.sort() kết hợp với bộ so sánh Comparator.comparingInt(Seat::getSeatId), đạt hiệu năng vượt trội $O(N \log N)$.</t>
+  </si>
+  <si>
+    <t>Ảnh chụp màn hình Git Diff mã nguồn sắp xếp</t>
+  </si>
+  <si>
+    <t>AI tự viết một đoạn code thủ công sử dụng thuật toán sắp xếp nổi bọt (Bubble Sort) với 2 vòng lặp lồng nhau để hoán đổi vị trí các phần tử ghế trong List.</t>
+  </si>
+  <si>
+    <t>Thuật toán Bubble Sort có độ phức tạp hiệu năng tệ ($O(N^2)$), gây giật lag và đơ ứng dụng khi chạy tập dữ liệu lớn. Java đã tối ưu hóa việc này thông qua thuật toán Dual-Pivot Quicksort trong thư viện Collections.sort().</t>
+  </si>
+  <si>
+    <t>Tôi phân tích thuật toán do AI sinh ra và nhận thấy nó gây lãng phí chu kỳ xử lý của CPU một cách không cần thiết, vi phạm tiêu chí tối ưu mã nguồn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tôi đã xóa bỏ hoàn toàn đoạn code thủ công lỗi thời này, thay thế bằng lệnh chuẩn Collections.sort() kết hợp với Comparator.comparingInt(), giúp code chạy mượt mà, đạt hiệu năng tối ưu $O(N \log N)$.</t>
   </si>
 </sst>
 </file>
@@ -726,11 +771,11 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -806,14 +851,14 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -870,7 +915,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -928,22 +973,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -952,6 +981,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1256,7 +1304,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
@@ -1265,22 +1313,22 @@
     <col min="5" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+    </row>
+    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1288,7 +1336,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1296,7 +1344,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -1304,7 +1352,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -1312,12 +1360,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -1325,7 +1373,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
@@ -1333,7 +1381,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
@@ -1345,7 +1393,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>17</v>
       </c>
@@ -1353,12 +1401,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>20</v>
       </c>
@@ -1372,7 +1420,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>24</v>
       </c>
@@ -1386,7 +1434,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>28</v>
       </c>
@@ -1400,7 +1448,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>32</v>
       </c>
@@ -1414,7 +1462,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>35</v>
       </c>
@@ -1422,12 +1470,12 @@
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>37</v>
       </c>
@@ -1438,7 +1486,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>40</v>
       </c>
@@ -1449,7 +1497,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>42</v>
       </c>
@@ -1460,7 +1508,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>43</v>
       </c>
@@ -1471,7 +1519,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>44</v>
       </c>
@@ -1493,7 +1541,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="18" customWidth="1"/>
@@ -1504,31 +1552,31 @@
     <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-    </row>
-    <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="29" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+    </row>
+    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-    </row>
-    <row r="3" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+    </row>
+    <row r="3" spans="1:8" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>47</v>
       </c>
@@ -1554,7 +1602,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="99.95" customHeight="1">
+    <row r="4" spans="1:8" ht="99.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>55</v>
       </c>
@@ -1580,7 +1628,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="99.95" customHeight="1">
+    <row r="5" spans="1:8" ht="99.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>62</v>
       </c>
@@ -1606,7 +1654,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="99.95" customHeight="1">
+    <row r="6" spans="1:8" ht="99.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>69</v>
       </c>
@@ -1632,7 +1680,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="7" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>4</v>
       </c>
@@ -1658,7 +1706,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="8" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>5</v>
       </c>
@@ -1684,7 +1732,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="9" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>6</v>
       </c>
@@ -1710,7 +1758,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="10" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>7</v>
       </c>
@@ -1736,7 +1784,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="11" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>8</v>
       </c>
@@ -1762,7 +1810,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="12" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>9</v>
       </c>
@@ -1788,7 +1836,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="13" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>10</v>
       </c>
@@ -1807,14 +1855,14 @@
       <c r="F13" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="G13" s="25" t="s">
         <v>110</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="14" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>11</v>
       </c>
@@ -1833,14 +1881,14 @@
       <c r="F14" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="21" t="s">
         <v>115</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="15" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>12</v>
       </c>
@@ -1866,7 +1914,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="16" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>13</v>
       </c>
@@ -1885,14 +1933,14 @@
       <c r="F16" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G16" s="33" t="s">
+      <c r="G16" s="27" t="s">
         <v>125</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="17" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>14</v>
       </c>
@@ -1914,31 +1962,63 @@
       <c r="G17" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="H17" s="32" t="s">
+      <c r="H17" s="21" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="18" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>15</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
+        <v>16</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="H19" s="34" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1948,7 +2028,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="21" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -1958,7 +2038,7 @@
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
     </row>
-    <row r="22" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="22" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -1968,7 +2048,7 @@
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
     </row>
-    <row r="23" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="23" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -1978,7 +2058,7 @@
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
     </row>
-    <row r="24" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="24" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -1988,7 +2068,7 @@
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
     </row>
-    <row r="25" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="25" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -1998,7 +2078,7 @@
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
     </row>
-    <row r="26" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="26" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -2020,34 +2100,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="25" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-    </row>
-    <row r="3" spans="1:6" ht="39.950000000000003" customHeight="1">
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+    </row>
+    <row r="3" spans="1:6" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>135</v>
       </c>
@@ -2067,7 +2147,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="60" customHeight="1">
+    <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>69</v>
       </c>
@@ -2087,7 +2167,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="91.5">
+    <row r="5" spans="1:6" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -2107,7 +2187,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="60" customHeight="1">
+    <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>8</v>
       </c>
@@ -2127,7 +2207,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1">
+    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>10</v>
       </c>
@@ -2147,7 +2227,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="60" customHeight="1">
+    <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>11</v>
       </c>
@@ -2167,7 +2247,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1">
+    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>13</v>
       </c>
@@ -2187,15 +2267,27 @@
         <v>167</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="60" customHeight="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-    </row>
-    <row r="11" spans="1:6" ht="60" customHeight="1">
+    <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>16</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -2203,7 +2295,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:6" ht="60" customHeight="1">
+    <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -2211,7 +2303,7 @@
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
     </row>
-    <row r="13" spans="1:6" ht="60" customHeight="1">
+    <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -2219,7 +2311,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="1:6" ht="60" customHeight="1">
+    <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -2227,7 +2319,7 @@
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" spans="1:6" ht="60" customHeight="1">
+    <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -2235,7 +2327,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="1:6" ht="60" customHeight="1">
+    <row r="16" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -2243,7 +2335,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
     </row>
-    <row r="17" spans="1:6" ht="60" customHeight="1">
+    <row r="17" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -2251,7 +2343,7 @@
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:6" ht="60" customHeight="1">
+    <row r="18" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -2259,7 +2351,7 @@
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="1:6" ht="60" customHeight="1">
+    <row r="19" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -2267,7 +2359,7 @@
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" ht="60" customHeight="1">
+    <row r="20" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -2275,7 +2367,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="1:6" ht="60" customHeight="1">
+    <row r="21" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -2283,7 +2375,7 @@
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="1:6" ht="60" customHeight="1">
+    <row r="22" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -2291,7 +2383,7 @@
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:6" ht="60" customHeight="1">
+    <row r="23" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -2299,7 +2391,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="1:6" ht="60" customHeight="1">
+    <row r="24" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -2307,12 +2399,12 @@
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>169</v>
       </c>
@@ -2323,7 +2415,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>141</v>
       </c>
@@ -2334,7 +2426,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>151</v>
       </c>
@@ -2345,7 +2437,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>146</v>
       </c>
@@ -2356,7 +2448,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>178</v>
       </c>
@@ -2367,7 +2459,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>181</v>
       </c>
@@ -2390,7 +2482,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
@@ -2398,28 +2490,28 @@
     <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
         <v>184</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="30" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+    </row>
+    <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>187</v>
       </c>
@@ -2433,7 +2525,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>191</v>
       </c>
@@ -2445,7 +2537,7 @@
       </c>
       <c r="D6" s="13"/>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>194</v>
       </c>
@@ -2457,7 +2549,7 @@
       </c>
       <c r="D7" s="13"/>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>196</v>
       </c>
@@ -2469,7 +2561,7 @@
       </c>
       <c r="D8" s="13"/>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>198</v>
       </c>
@@ -2481,7 +2573,7 @@
       </c>
       <c r="D9" s="13"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>200</v>
       </c>
@@ -2493,12 +2585,12 @@
       </c>
       <c r="D10" s="13"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>187</v>
       </c>
@@ -2512,7 +2604,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>191</v>
       </c>
@@ -2524,7 +2616,7 @@
       </c>
       <c r="D14" s="13"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>194</v>
       </c>
@@ -2536,7 +2628,7 @@
       </c>
       <c r="D15" s="13"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>196</v>
       </c>
@@ -2548,7 +2640,7 @@
       </c>
       <c r="D16" s="13"/>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>198</v>
       </c>
@@ -2560,7 +2652,7 @@
       </c>
       <c r="D17" s="13"/>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>200</v>
       </c>
@@ -2572,32 +2664,32 @@
       </c>
       <c r="D18" s="13"/>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>47</v>
       </c>
@@ -2611,7 +2703,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>55</v>
       </c>
@@ -2619,7 +2711,7 @@
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>62</v>
       </c>
@@ -2627,7 +2719,7 @@
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>69</v>
       </c>

--- a/ai_logs/VoXuanLong_Ai_Log.xlsx
+++ b/ai_logs/VoXuanLong_Ai_Log.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NHOM_04_LAB211_TicketBooking\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EEB6DEB-FC08-48AA-90C3-211A1E0F1CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CA2B86C-6CB0-44BD-98DD-EE01AF72E562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -470,6 +470,36 @@
     <t>Ảnh chụp màn hình Log lỗi ngoại lệ</t>
   </si>
   <si>
+    <t>Xây dựng tính năng tìm kiếm một chiếc ghế cụ thể theo mã ID (seatId) một cách tối ưu ở tầng Service/Repository khi dữ liệu lớn đã được nạp lên RAM.</t>
+  </si>
+  <si>
+    <t>"Hãy viết cho tôi hàm tìm kiếm một chiếc ghế theo ID từ danh sách 5000 ghế trên RAM."</t>
+  </si>
+  <si>
+    <t>AI cung cấp một hàm sử dụng vòng lặp duyệt tuần tự (Linear Search) chạy từ đầu đến cuối danh sách List để so sánh ID từng ghế.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Phát hiện duyệt tuần tự bằng vòng lặp qua một ArrayList cực kỳ kém tối ưu đối với các thao tác tìm kiếm được gọi lặp đi lặp lại nhiều lần, có độ phức tạp thuật toán là $O(N)$. Nếu hệ thống có nhiều lượt truy cập tra cứu ghế cùng lúc sẽ bị trễ.Contextualization: Đồ án rạp phim đòi hỏi thao tác khách hàng click chọn ghế hoặc tra cứu thông tin trạng thái ghế phải phản hồi ngay lập tức.Creative Synthesis: Chuyển đổi cấu trúc lưu trữ từ dạng danh sách phẳng sang cấu trúc ánh xạ để tận dụng cơ chế băm dữ liệu.Decision: Tự tối ưu lại bằng cách lưu trữ danh sách ghế vào một cấu trúc HashMap&lt;Integer, Seat&gt; ngay khi đọc file CSV lên RAM. Khi cần tìm kiếm, chỉ cần gọi hàm map.get(id) đạt độ phức tạp tuyệt đối $O(1)$ - tra cứu tức thì không độ trễ.</t>
+  </si>
+  <si>
+    <t>Ảnh chụp màn hình Code hàm tìm kiếm tối ưu</t>
+  </si>
+  <si>
+    <t>Thực hiện sắp xếp (Sort) lại danh sách ghế đang bị lộn xộn theo thứ tự tăng dần của mã ID trước khi hiển thị lên giao diện Terminal hoặc xuất báo cáo.</t>
+  </si>
+  <si>
+    <t>"Làm sao để sắp xếp danh sách ghế lộn xộn trong List theo thứ tự ID tăng dần?"</t>
+  </si>
+  <si>
+    <t>AI tự viết một đoạn code thủ công dài dòng sử dụng thuật toán sắp xếp nổi bọt (Bubble Sort) với 2 vòng lặp lồng nhau để hoán đổi vị trí các phần tử ghế.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Nhận ra AI đang mắc lỗi đơn giản hóa quá mức (Oversimplification). Thuật toán Bubble Sort có hiệu năng rất tệ $O(N^2)$, hoàn toàn lỗi thời và lãng phí tài nguyên CPU khi xử lý tập dữ liệu lớn, trong khi Java đã tích hợp sẵn các bộ thư viện cực mạnh.Contextualization: Yêu cầu mã nguồn đồ án phải đạt tiêu chuẩn chuyên nghiệp, tinh gọn và tận dụng tối đa sức mạnh API sẵn có của Java Collection Framework.Creative Synthesis: Sử dụng bộ so sánh Comparator kết hợp với biểu thức Lambda để thay thế hoàn toàn các vòng lặp hoán đổi vị trí thủ công.Decision: Bác bỏ hoàn toàn đoạn code sắp xếp thủ công của AI. Thay thế bằng giải pháp chuẩn công nghiệp: sử dụng phương thức Collections.sort() kết hợp với bộ so sánh Comparator.comparingInt(Seat::getSeatId), đạt hiệu năng vượt trội $O(N \log N)$.</t>
+  </si>
+  <si>
+    <t>Ảnh chụp màn hình Git Diff mã nguồn sắp xếp</t>
+  </si>
+  <si>
     <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
   </si>
   <si>
@@ -575,6 +605,18 @@
     <t>Tôi chủ động thay thế FileWriter bằng BufferedWriter để gom toàn bộ dữ liệu ghi 1 lần duy nhất, đẩy tốc độ xử lý tăng vọt và hạ thời gian xuống còn ~100ms.</t>
   </si>
   <si>
+    <t>AI tự viết một đoạn code thủ công sử dụng thuật toán sắp xếp nổi bọt (Bubble Sort) với 2 vòng lặp lồng nhau để hoán đổi vị trí các phần tử ghế trong List.</t>
+  </si>
+  <si>
+    <t>Thuật toán Bubble Sort có độ phức tạp hiệu năng tệ ($O(N^2)$), gây giật lag và đơ ứng dụng khi chạy tập dữ liệu lớn. Java đã tối ưu hóa việc này thông qua thuật toán Dual-Pivot Quicksort trong thư viện Collections.sort().</t>
+  </si>
+  <si>
+    <t>Tôi phân tích thuật toán do AI sinh ra và nhận thấy nó gây lãng phí chu kỳ xử lý của CPU một cách không cần thiết, vi phạm tiêu chí tối ưu mã nguồn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tôi đã xóa bỏ hoàn toàn đoạn code thủ công lỗi thời này, thay thế bằng lệnh chuẩn Collections.sort() kết hợp với Comparator.comparingInt(), giúp code chạy mượt mà, đạt hiệu năng tối ưu $O(N \log N)$.</t>
+  </si>
+  <si>
     <t>HALLUCINATION TYPES REFERENCE:</t>
   </si>
   <si>
@@ -720,48 +762,6 @@
   </si>
   <si>
     <t>Tôi có evidence?</t>
-  </si>
-  <si>
-    <t>Xây dựng tính năng tìm kiếm một chiếc ghế cụ thể theo mã ID (seatId) một cách tối ưu ở tầng Service/Repository khi dữ liệu lớn đã được nạp lên RAM.</t>
-  </si>
-  <si>
-    <t>"Hãy viết cho tôi hàm tìm kiếm một chiếc ghế theo ID từ danh sách 5000 ghế trên RAM."</t>
-  </si>
-  <si>
-    <t>AI cung cấp một hàm sử dụng vòng lặp duyệt tuần tự (Linear Search) chạy từ đầu đến cuối danh sách List để so sánh ID từng ghế.</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Phát hiện duyệt tuần tự bằng vòng lặp qua một ArrayList cực kỳ kém tối ưu đối với các thao tác tìm kiếm được gọi lặp đi lặp lại nhiều lần, có độ phức tạp thuật toán là $O(N)$. Nếu hệ thống có nhiều lượt truy cập tra cứu ghế cùng lúc sẽ bị trễ.Contextualization: Đồ án rạp phim đòi hỏi thao tác khách hàng click chọn ghế hoặc tra cứu thông tin trạng thái ghế phải phản hồi ngay lập tức.Creative Synthesis: Chuyển đổi cấu trúc lưu trữ từ dạng danh sách phẳng sang cấu trúc ánh xạ để tận dụng cơ chế băm dữ liệu.Decision: Tự tối ưu lại bằng cách lưu trữ danh sách ghế vào một cấu trúc HashMap&lt;Integer, Seat&gt; ngay khi đọc file CSV lên RAM. Khi cần tìm kiếm, chỉ cần gọi hàm map.get(id) đạt độ phức tạp tuyệt đối $O(1)$ - tra cứu tức thì không độ trễ.</t>
-  </si>
-  <si>
-    <t>Ảnh chụp màn hình Code hàm tìm kiếm tối ưu</t>
-  </si>
-  <si>
-    <t>Thực hiện sắp xếp (Sort) lại danh sách ghế đang bị lộn xộn theo thứ tự tăng dần của mã ID trước khi hiển thị lên giao diện Terminal hoặc xuất báo cáo.</t>
-  </si>
-  <si>
-    <t>"Làm sao để sắp xếp danh sách ghế lộn xộn trong List theo thứ tự ID tăng dần?"</t>
-  </si>
-  <si>
-    <t>AI tự viết một đoạn code thủ công dài dòng sử dụng thuật toán sắp xếp nổi bọt (Bubble Sort) với 2 vòng lặp lồng nhau để hoán đổi vị trí các phần tử ghế.</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Nhận ra AI đang mắc lỗi đơn giản hóa quá mức (Oversimplification). Thuật toán Bubble Sort có hiệu năng rất tệ $O(N^2)$, hoàn toàn lỗi thời và lãng phí tài nguyên CPU khi xử lý tập dữ liệu lớn, trong khi Java đã tích hợp sẵn các bộ thư viện cực mạnh.Contextualization: Yêu cầu mã nguồn đồ án phải đạt tiêu chuẩn chuyên nghiệp, tinh gọn và tận dụng tối đa sức mạnh API sẵn có của Java Collection Framework.Creative Synthesis: Sử dụng bộ so sánh Comparator kết hợp với biểu thức Lambda để thay thế hoàn toàn các vòng lặp hoán đổi vị trí thủ công.Decision: Bác bỏ hoàn toàn đoạn code sắp xếp thủ công của AI. Thay thế bằng giải pháp chuẩn công nghiệp: sử dụng phương thức Collections.sort() kết hợp với bộ so sánh Comparator.comparingInt(Seat::getSeatId), đạt hiệu năng vượt trội $O(N \log N)$.</t>
-  </si>
-  <si>
-    <t>Ảnh chụp màn hình Git Diff mã nguồn sắp xếp</t>
-  </si>
-  <si>
-    <t>AI tự viết một đoạn code thủ công sử dụng thuật toán sắp xếp nổi bọt (Bubble Sort) với 2 vòng lặp lồng nhau để hoán đổi vị trí các phần tử ghế trong List.</t>
-  </si>
-  <si>
-    <t>Thuật toán Bubble Sort có độ phức tạp hiệu năng tệ ($O(N^2)$), gây giật lag và đơ ứng dụng khi chạy tập dữ liệu lớn. Java đã tối ưu hóa việc này thông qua thuật toán Dual-Pivot Quicksort trong thư viện Collections.sort().</t>
-  </si>
-  <si>
-    <t>Tôi phân tích thuật toán do AI sinh ra và nhận thấy nó gây lãng phí chu kỳ xử lý của CPU một cách không cần thiết, vi phạm tiêu chí tối ưu mã nguồn.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tôi đã xóa bỏ hoàn toàn đoạn code thủ công lỗi thời này, thay thế bằng lệnh chuẩn Collections.sort() kết hợp với Comparator.comparingInt(), giúp code chạy mượt mà, đạt hiệu năng tối ưu $O(N \log N)$.</t>
   </si>
 </sst>
 </file>
@@ -771,7 +771,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -915,7 +915,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -982,10 +982,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -998,9 +1001,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -1304,7 +1305,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
@@ -1313,100 +1314,146 @@
     <col min="5" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-    </row>
-    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+    </row>
+    <row r="3" spans="1:6" ht="18">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+    </row>
+    <row r="4" spans="1:6" ht="14.45">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4" s="28"/>
+      <c r="C4" s="28" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+    </row>
+    <row r="5" spans="1:6" ht="14.45">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B5" s="28"/>
+      <c r="C5" s="28" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+    </row>
+    <row r="6" spans="1:6" ht="14.45">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6" s="28"/>
+      <c r="C6" s="28" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+    </row>
+    <row r="7" spans="1:6" ht="14.45">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B7" s="28"/>
+      <c r="C7" s="28" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+    </row>
+    <row r="9" spans="1:6" ht="18">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+    </row>
+    <row r="10" spans="1:6" ht="14.45">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B10" s="28"/>
+      <c r="C10" s="28" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+    </row>
+    <row r="11" spans="1:6" ht="14.45">
       <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="B11" s="28"/>
       <c r="C11" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+    </row>
+    <row r="12" spans="1:6" ht="14.45">
       <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="B12" s="28"/>
       <c r="C12" s="4" t="e">
         <f>C11/C10</f>
         <v>#VALUE!</v>
       </c>
+      <c r="D12" s="28"/>
       <c r="E12" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="F12" s="28"/>
+    </row>
+    <row r="13" spans="1:6" ht="14.45">
       <c r="A13" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="B13" s="28"/>
       <c r="C13" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+    </row>
+    <row r="15" spans="1:6" ht="18">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+    </row>
+    <row r="16" spans="1:6" ht="14.45">
       <c r="A16" s="6" t="s">
         <v>20</v>
       </c>
@@ -1419,8 +1466,10 @@
       <c r="D16" s="6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="7" t="s">
         <v>24</v>
       </c>
@@ -1434,7 +1483,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4">
       <c r="A18" s="7" t="s">
         <v>28</v>
       </c>
@@ -1448,7 +1497,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4">
       <c r="A19" s="7" t="s">
         <v>32</v>
       </c>
@@ -1462,7 +1511,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4">
       <c r="A20" s="7" t="s">
         <v>35</v>
       </c>
@@ -1470,12 +1519,15 @@
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
     </row>
-    <row r="22" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" ht="18">
       <c r="A22" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+    </row>
+    <row r="23" spans="1:4" ht="14.45">
       <c r="A23" s="6" t="s">
         <v>37</v>
       </c>
@@ -1485,8 +1537,9 @@
       <c r="C23" s="6" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D23" s="28"/>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" s="7" t="s">
         <v>40</v>
       </c>
@@ -1496,8 +1549,9 @@
       <c r="C24" s="9" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D24" s="28"/>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" s="7" t="s">
         <v>42</v>
       </c>
@@ -1507,8 +1561,9 @@
       <c r="C25" s="9" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D25" s="28"/>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" s="7" t="s">
         <v>43</v>
       </c>
@@ -1518,8 +1573,9 @@
       <c r="C26" s="9" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D26" s="28"/>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" s="7" t="s">
         <v>44</v>
       </c>
@@ -1529,6 +1585,7 @@
       <c r="C27" s="9" t="s">
         <v>41</v>
       </c>
+      <c r="D27" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1541,7 +1598,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="18" customWidth="1"/>
@@ -1552,31 +1609,31 @@
     <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-    </row>
-    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+    </row>
+    <row r="2" spans="1:8" ht="30" customHeight="1">
+      <c r="A2" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-    </row>
-    <row r="3" spans="1:8" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+    </row>
+    <row r="3" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>47</v>
       </c>
@@ -1602,7 +1659,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="99.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="99.95" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>55</v>
       </c>
@@ -1628,7 +1685,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="99.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="99.95" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>62</v>
       </c>
@@ -1654,7 +1711,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="99.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="99.95" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>69</v>
       </c>
@@ -1680,7 +1737,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A7" s="7">
         <v>4</v>
       </c>
@@ -1706,7 +1763,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A8" s="7">
         <v>5</v>
       </c>
@@ -1732,7 +1789,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A9" s="7">
         <v>6</v>
       </c>
@@ -1758,7 +1815,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A10" s="7">
         <v>7</v>
       </c>
@@ -1784,7 +1841,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A11" s="7">
         <v>8</v>
       </c>
@@ -1810,7 +1867,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A12" s="7">
         <v>9</v>
       </c>
@@ -1836,7 +1893,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A13" s="7">
         <v>10</v>
       </c>
@@ -1862,7 +1919,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A14" s="7">
         <v>11</v>
       </c>
@@ -1888,7 +1945,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A15" s="7">
         <v>12</v>
       </c>
@@ -1914,7 +1971,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A16" s="7">
         <v>13</v>
       </c>
@@ -1940,7 +1997,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A17" s="7">
         <v>14</v>
       </c>
@@ -1966,7 +2023,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A18" s="7">
         <v>15</v>
       </c>
@@ -1977,22 +2034,22 @@
         <v>44</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>217</v>
+        <v>133</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>218</v>
+        <v>134</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>219</v>
+        <v>135</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>220</v>
+        <v>136</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A19" s="7">
         <v>16</v>
       </c>
@@ -2003,22 +2060,22 @@
         <v>44</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>222</v>
+        <v>138</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>223</v>
+        <v>139</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>224</v>
+        <v>140</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="H19" s="34" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="H19" s="29" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -2028,7 +2085,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -2038,7 +2095,7 @@
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
     </row>
-    <row r="22" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -2048,7 +2105,7 @@
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
     </row>
-    <row r="23" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -2058,7 +2115,7 @@
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
     </row>
-    <row r="24" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -2068,7 +2125,7 @@
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
     </row>
-    <row r="25" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -2078,7 +2135,7 @@
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
     </row>
-    <row r="26" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -2100,194 +2157,194 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-    </row>
-    <row r="3" spans="1:6" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
+      <c r="A1" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+    </row>
+    <row r="3" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="60" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>69</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="82.8" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="82.9">
       <c r="A5" s="7">
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="60" customHeight="1">
       <c r="A6" s="7">
         <v>8</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="60" customHeight="1">
       <c r="A7" s="7">
         <v>10</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="60" customHeight="1">
       <c r="A8" s="7">
         <v>11</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="60" customHeight="1">
       <c r="A9" s="7">
         <v>13</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="60" customHeight="1">
       <c r="A10" s="7">
         <v>16</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>227</v>
+        <v>178</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>228</v>
+        <v>179</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>229</v>
+        <v>180</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="60" customHeight="1">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -2295,7 +2352,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="60" customHeight="1">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -2303,7 +2360,7 @@
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
     </row>
-    <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="60" customHeight="1">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -2311,7 +2368,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="60" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -2319,7 +2376,7 @@
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="60" customHeight="1">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -2327,7 +2384,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="60" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -2335,7 +2392,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
     </row>
-    <row r="17" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="60" customHeight="1">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -2343,7 +2400,7 @@
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="60" customHeight="1">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -2351,7 +2408,7 @@
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="60" customHeight="1">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -2359,7 +2416,7 @@
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="60" customHeight="1">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -2367,7 +2424,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="60" customHeight="1">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -2375,7 +2432,7 @@
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="60" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -2383,7 +2440,7 @@
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="60" customHeight="1">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -2391,7 +2448,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="60" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -2399,75 +2456,86 @@
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
     </row>
-    <row r="30" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="18">
       <c r="A30" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+    </row>
+    <row r="31" spans="1:6" ht="14.45">
       <c r="A31" s="10" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+    </row>
+    <row r="32" spans="1:6" ht="27.6">
       <c r="A32" s="7" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+    </row>
+    <row r="33" spans="1:3" ht="27.6">
       <c r="A33" s="7" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="27.6">
       <c r="A34" s="7" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="27.6">
       <c r="A35" s="7" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="41.45">
       <c r="A36" s="7" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -2482,7 +2550,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
@@ -2490,220 +2558,241 @@
     <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
-        <v>184</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-    </row>
-    <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4">
+      <c r="A1" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+    </row>
+    <row r="4" spans="1:4" ht="18">
       <c r="A4" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+    </row>
+    <row r="5" spans="1:4" ht="14.45">
       <c r="A5" s="6" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="12" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="D6" s="13"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" s="12" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="D7" s="13"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" s="12" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="D8" s="13"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" s="12" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="D9" s="13"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B10" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="D10" s="13"/>
+    </row>
+    <row r="12" spans="1:4" ht="18">
+      <c r="A12" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+    </row>
+    <row r="13" spans="1:4" ht="14.45">
+      <c r="A13" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="D10" s="13"/>
-    </row>
-    <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
+      <c r="B13" s="11" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>188</v>
-      </c>
       <c r="C13" s="6" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="12" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="D14" s="13"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="D15" s="13"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16" s="12" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="D16" s="13"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4">
       <c r="A17" s="12" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="B17" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>193</v>
-      </c>
       <c r="D17" s="13"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4">
       <c r="A18" s="12" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="D18" s="13"/>
     </row>
-    <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="15.6">
       <c r="A20" s="14" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+    </row>
+    <row r="21" spans="1:4" ht="14.45">
       <c r="A21" s="15" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+      <c r="B21" s="28"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+    </row>
+    <row r="22" spans="1:4" ht="14.45">
       <c r="A22" s="15" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+        <v>225</v>
+      </c>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+    </row>
+    <row r="25" spans="1:4" ht="18">
       <c r="A25" s="1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+    </row>
+    <row r="26" spans="1:4" ht="14.45">
       <c r="A26" s="16" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+    </row>
+    <row r="27" spans="1:4" ht="43.15">
       <c r="A27" s="17" t="s">
         <v>47</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" s="9" t="s">
         <v>55</v>
       </c>
@@ -2711,7 +2800,7 @@
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4">
       <c r="A29" s="9" t="s">
         <v>62</v>
       </c>
@@ -2719,7 +2808,7 @@
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4">
       <c r="A30" s="9" t="s">
         <v>69</v>
       </c>

--- a/ai_logs/VoXuanLong_Ai_Log.xlsx
+++ b/ai_logs/VoXuanLong_Ai_Log.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -771,7 +771,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -915,7 +915,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -982,13 +982,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1001,7 +1001,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -1305,7 +1304,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
@@ -1314,146 +1313,100 @@
     <col min="5" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-    </row>
-    <row r="3" spans="1:6" ht="18">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+    </row>
+    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-    </row>
-    <row r="4" spans="1:6" ht="14.45">
+    </row>
+    <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-    </row>
-    <row r="5" spans="1:6" ht="14.45">
+    </row>
+    <row r="5" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28" t="s">
+      <c r="C5" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-    </row>
-    <row r="6" spans="1:6" ht="14.45">
+    </row>
+    <row r="6" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28" t="s">
+      <c r="C6" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-    </row>
-    <row r="7" spans="1:6" ht="14.45">
+    </row>
+    <row r="7" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28" t="s">
+      <c r="C7" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-    </row>
-    <row r="9" spans="1:6" ht="18">
+    </row>
+    <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-    </row>
-    <row r="10" spans="1:6" ht="14.45">
+    </row>
+    <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28" t="s">
+      <c r="C10" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-    </row>
-    <row r="11" spans="1:6" ht="14.45">
+    </row>
+    <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="28"/>
       <c r="C11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-    </row>
-    <row r="12" spans="1:6" ht="14.45">
+    </row>
+    <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="28"/>
       <c r="C12" s="4" t="e">
         <f>C11/C10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D12" s="28"/>
       <c r="E12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="28"/>
-    </row>
-    <row r="13" spans="1:6" ht="14.45">
+    </row>
+    <row r="13" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="28"/>
       <c r="C13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-    </row>
-    <row r="15" spans="1:6" ht="18">
+    </row>
+    <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-    </row>
-    <row r="16" spans="1:6" ht="14.45">
+    </row>
+    <row r="16" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>20</v>
       </c>
@@ -1466,10 +1419,8 @@
       <c r="D16" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-    </row>
-    <row r="17" spans="1:4">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>24</v>
       </c>
@@ -1483,7 +1434,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>28</v>
       </c>
@@ -1497,7 +1448,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>32</v>
       </c>
@@ -1511,7 +1462,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>35</v>
       </c>
@@ -1519,15 +1470,12 @@
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
     </row>
-    <row r="22" spans="1:4" ht="18">
+    <row r="22" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-    </row>
-    <row r="23" spans="1:4" ht="14.45">
+    </row>
+    <row r="23" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>37</v>
       </c>
@@ -1537,9 +1485,8 @@
       <c r="C23" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="28"/>
-    </row>
-    <row r="24" spans="1:4">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>40</v>
       </c>
@@ -1549,9 +1496,8 @@
       <c r="C24" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D24" s="28"/>
-    </row>
-    <row r="25" spans="1:4">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>42</v>
       </c>
@@ -1561,9 +1507,8 @@
       <c r="C25" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="28"/>
-    </row>
-    <row r="26" spans="1:4">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>43</v>
       </c>
@@ -1573,9 +1518,8 @@
       <c r="C26" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D26" s="28"/>
-    </row>
-    <row r="27" spans="1:4">
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>44</v>
       </c>
@@ -1585,7 +1529,6 @@
       <c r="C27" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1598,7 +1541,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="18" customWidth="1"/>
@@ -1609,31 +1552,31 @@
     <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-    </row>
-    <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+    </row>
+    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-    </row>
-    <row r="3" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+    </row>
+    <row r="3" spans="1:8" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>47</v>
       </c>
@@ -1659,7 +1602,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="99.95" customHeight="1">
+    <row r="4" spans="1:8" ht="99.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>55</v>
       </c>
@@ -1685,7 +1628,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="99.95" customHeight="1">
+    <row r="5" spans="1:8" ht="99.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>62</v>
       </c>
@@ -1711,7 +1654,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="99.95" customHeight="1">
+    <row r="6" spans="1:8" ht="99.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>69</v>
       </c>
@@ -1737,7 +1680,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="7" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>4</v>
       </c>
@@ -1763,7 +1706,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="8" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>5</v>
       </c>
@@ -1789,7 +1732,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="9" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>6</v>
       </c>
@@ -1815,7 +1758,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="10" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>7</v>
       </c>
@@ -1841,7 +1784,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="11" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>8</v>
       </c>
@@ -1867,7 +1810,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="12" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>9</v>
       </c>
@@ -1893,7 +1836,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="13" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>10</v>
       </c>
@@ -1919,7 +1862,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="14" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>11</v>
       </c>
@@ -1945,7 +1888,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="15" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>12</v>
       </c>
@@ -1971,7 +1914,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="16" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>13</v>
       </c>
@@ -1997,7 +1940,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="17" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>14</v>
       </c>
@@ -2023,7 +1966,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="18" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>15</v>
       </c>
@@ -2049,7 +1992,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="19" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>16</v>
       </c>
@@ -2071,11 +2014,11 @@
       <c r="G19" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="H19" s="29" t="s">
+      <c r="H19" s="28" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="20" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -2085,7 +2028,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="21" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -2095,7 +2038,7 @@
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
     </row>
-    <row r="22" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="22" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -2105,7 +2048,7 @@
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
     </row>
-    <row r="23" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="23" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -2115,7 +2058,7 @@
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
     </row>
-    <row r="24" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="24" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -2125,7 +2068,7 @@
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
     </row>
-    <row r="25" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="25" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -2135,7 +2078,7 @@
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
     </row>
-    <row r="26" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="26" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -2157,34 +2100,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-    </row>
-    <row r="3" spans="1:6" ht="39.950000000000003" customHeight="1">
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+    </row>
+    <row r="3" spans="1:6" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>145</v>
       </c>
@@ -2204,7 +2147,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="60" customHeight="1">
+    <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>69</v>
       </c>
@@ -2224,7 +2167,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="82.9">
+    <row r="5" spans="1:6" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -2244,7 +2187,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="60" customHeight="1">
+    <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>8</v>
       </c>
@@ -2264,7 +2207,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1">
+    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>10</v>
       </c>
@@ -2284,7 +2227,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="60" customHeight="1">
+    <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>11</v>
       </c>
@@ -2304,7 +2247,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1">
+    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>13</v>
       </c>
@@ -2324,7 +2267,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="60" customHeight="1">
+    <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>16</v>
       </c>
@@ -2344,7 +2287,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="60" customHeight="1">
+    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -2352,7 +2295,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:6" ht="60" customHeight="1">
+    <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -2360,7 +2303,7 @@
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
     </row>
-    <row r="13" spans="1:6" ht="60" customHeight="1">
+    <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -2368,7 +2311,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="1:6" ht="60" customHeight="1">
+    <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -2376,7 +2319,7 @@
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" spans="1:6" ht="60" customHeight="1">
+    <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -2384,7 +2327,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="1:6" ht="60" customHeight="1">
+    <row r="16" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -2392,7 +2335,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
     </row>
-    <row r="17" spans="1:6" ht="60" customHeight="1">
+    <row r="17" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -2400,7 +2343,7 @@
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:6" ht="60" customHeight="1">
+    <row r="18" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -2408,7 +2351,7 @@
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="1:6" ht="60" customHeight="1">
+    <row r="19" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -2416,7 +2359,7 @@
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" ht="60" customHeight="1">
+    <row r="20" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -2424,7 +2367,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="1:6" ht="60" customHeight="1">
+    <row r="21" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -2432,7 +2375,7 @@
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="1:6" ht="60" customHeight="1">
+    <row r="22" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -2440,7 +2383,7 @@
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:6" ht="60" customHeight="1">
+    <row r="23" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -2448,7 +2391,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="1:6" ht="60" customHeight="1">
+    <row r="24" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -2456,17 +2399,12 @@
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
     </row>
-    <row r="30" spans="1:6" ht="18">
+    <row r="30" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-    </row>
-    <row r="31" spans="1:6" ht="14.45">
+    </row>
+    <row r="31" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>183</v>
       </c>
@@ -2476,11 +2414,8 @@
       <c r="C31" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-    </row>
-    <row r="32" spans="1:6" ht="27.6">
+    </row>
+    <row r="32" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>151</v>
       </c>
@@ -2490,11 +2425,8 @@
       <c r="C32" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-    </row>
-    <row r="33" spans="1:3" ht="27.6">
+    </row>
+    <row r="33" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>161</v>
       </c>
@@ -2505,7 +2437,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="27.6">
+    <row r="34" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>156</v>
       </c>
@@ -2516,7 +2448,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="27.6">
+    <row r="35" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>192</v>
       </c>
@@ -2527,7 +2459,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="41.45">
+    <row r="36" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>195</v>
       </c>
@@ -2550,7 +2482,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
@@ -2558,31 +2490,28 @@
     <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
         <v>199</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-    </row>
-    <row r="4" spans="1:4" ht="18">
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+    </row>
+    <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-    </row>
-    <row r="5" spans="1:4" ht="14.45">
+    </row>
+    <row r="5" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>201</v>
       </c>
@@ -2596,7 +2525,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>205</v>
       </c>
@@ -2608,7 +2537,7 @@
       </c>
       <c r="D6" s="13"/>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>208</v>
       </c>
@@ -2620,7 +2549,7 @@
       </c>
       <c r="D7" s="13"/>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>210</v>
       </c>
@@ -2632,7 +2561,7 @@
       </c>
       <c r="D8" s="13"/>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>212</v>
       </c>
@@ -2644,7 +2573,7 @@
       </c>
       <c r="D9" s="13"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>214</v>
       </c>
@@ -2656,15 +2585,12 @@
       </c>
       <c r="D10" s="13"/>
     </row>
-    <row r="12" spans="1:4" ht="18">
+    <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-    </row>
-    <row r="13" spans="1:4" ht="14.45">
+    </row>
+    <row r="13" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>201</v>
       </c>
@@ -2678,7 +2604,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>205</v>
       </c>
@@ -2690,7 +2616,7 @@
       </c>
       <c r="D14" s="13"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>208</v>
       </c>
@@ -2702,7 +2628,7 @@
       </c>
       <c r="D15" s="13"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>210</v>
       </c>
@@ -2714,7 +2640,7 @@
       </c>
       <c r="D16" s="13"/>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>212</v>
       </c>
@@ -2726,7 +2652,7 @@
       </c>
       <c r="D17" s="13"/>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>214</v>
       </c>
@@ -2738,47 +2664,32 @@
       </c>
       <c r="D18" s="13"/>
     </row>
-    <row r="20" spans="1:4" ht="15.6">
+    <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-    </row>
-    <row r="21" spans="1:4" ht="14.45">
+    </row>
+    <row r="21" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-    </row>
-    <row r="22" spans="1:4" ht="14.45">
+    </row>
+    <row r="22" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-    </row>
-    <row r="25" spans="1:4" ht="18">
+    </row>
+    <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-    </row>
-    <row r="26" spans="1:4" ht="14.45">
+    </row>
+    <row r="26" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-    </row>
-    <row r="27" spans="1:4" ht="43.15">
+    </row>
+    <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>47</v>
       </c>
@@ -2792,7 +2703,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>55</v>
       </c>
@@ -2800,7 +2711,7 @@
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>62</v>
       </c>
@@ -2808,7 +2719,7 @@
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>69</v>
       </c>

--- a/ai_logs/VoXuanLong_Ai_Log.xlsx
+++ b/ai_logs/VoXuanLong_Ai_Log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NHOM_04_LAB211_TicketBooking\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CA2B86C-6CB0-44BD-98DD-EE01AF72E562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F5AEEBA-AE27-45DB-8F1E-7188CC692CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="226">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -75,15 +75,9 @@
     <t>Total Prompts Used (all AI tools):</t>
   </si>
   <si>
-    <t>[e.g., ~150]</t>
-  </si>
-  <si>
     <t>Core Prompts Logged:</t>
   </si>
   <si>
-    <t>[e.g., 18]</t>
-  </si>
-  <si>
     <t>Selection Ratio:</t>
   </si>
   <si>
@@ -91,9 +85,6 @@
   </si>
   <si>
     <t>Hallucination Detected:</t>
-  </si>
-  <si>
-    <t>[Count]</t>
   </si>
   <si>
     <t>AI TOOLS USED</t>
@@ -416,9 +407,6 @@
     <t>Ảnh chụp màn hình Code</t>
   </si>
   <si>
-    <t>Data Evaluation</t>
-  </si>
-  <si>
     <t>Lựa chọn kiểu dữ liệu tối ưu cho các trường khóa chính và khóa ngoại (seatId và sectionRef) bên trong lớp thực thể Seat.java.</t>
   </si>
   <si>
@@ -448,9 +436,6 @@
   </si>
   <si>
     <t>Báo cáo số liệu hiệu năng (Metrics Log)</t>
-  </si>
-  <si>
-    <t>System Robustness</t>
   </si>
   <si>
     <t>Triển khai cơ chế bắt lỗi ngoại lệ (Exception Handling) để xử lý các tình huống file CSV đầu vào xuất hiện dòng trống hoặc dữ liệu bị lỗi định dạng.</t>
@@ -784,41 +769,48 @@
       <sz val="16"/>
       <color rgb="FF2E75B6"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF2E75B6"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -826,26 +818,31 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
@@ -859,6 +856,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1369,102 +1367,102 @@
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C10" t="s">
-        <v>12</v>
+      <c r="C10">
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="3">
         <v>13</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="4" t="e">
+        <v>13</v>
+      </c>
+      <c r="C12" s="4">
         <f>C11/C10</f>
-        <v>#VALUE!</v>
+        <v>0.18571428571428572</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="C13" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1472,62 +1470,62 @@
     </row>
     <row r="22" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B24" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B25" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B26" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B27" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1554,7 +1552,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="31" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -1566,7 +1564,7 @@
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -1578,106 +1576,106 @@
     </row>
     <row r="3" spans="1:8" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="99.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>58</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="99.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>65</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="99.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="G6" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>73</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1685,25 +1683,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="H7" s="20" t="s">
         <v>78</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H7" s="20" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1711,25 +1709,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="H8" s="22" t="s">
         <v>83</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="G8" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="H8" s="22" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1737,25 +1735,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G9" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="H9" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1763,25 +1761,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="H10" s="22" t="s">
         <v>93</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="H10" s="22" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1789,25 +1787,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="H11" s="23" t="s">
         <v>98</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="G11" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="H11" s="23" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1815,25 +1813,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D12" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="H12" s="7" t="s">
         <v>103</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="G12" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
@@ -1841,25 +1839,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="H13" s="7" t="s">
         <v>108</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="G13" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1867,25 +1865,25 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G14" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="H14" s="7" t="s">
         <v>113</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="G14" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1893,25 +1891,25 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="G15" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="G15" s="23" t="s">
-        <v>121</v>
-      </c>
       <c r="H15" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1919,25 +1917,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="D16" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>122</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="G16" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1945,25 +1943,25 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C17" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="H17" s="21" t="s">
         <v>127</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="G17" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="H17" s="21" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1971,25 +1969,25 @@
         <v>15</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1997,25 +1995,25 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H19" s="28" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -2109,7 +2107,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -2119,7 +2117,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -2129,42 +2127,42 @@
     </row>
     <row r="3" spans="1:6" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="82.8" x14ac:dyDescent="0.25">
@@ -2172,19 +2170,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2192,19 +2190,19 @@
         <v>8</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2212,19 +2210,19 @@
         <v>10</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2232,19 +2230,19 @@
         <v>11</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2252,19 +2250,19 @@
         <v>13</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2272,19 +2270,19 @@
         <v>16</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2401,73 +2399,73 @@
     </row>
     <row r="30" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -2492,7 +2490,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="31" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -2500,7 +2498,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -2508,204 +2506,204 @@
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D10" s="13"/>
     </row>
     <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D14" s="13"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D15" s="13"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D17" s="13"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D18" s="13"/>
     </row>
     <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -2713,7 +2711,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -2721,7 +2719,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>

--- a/ai_logs/VoXuanLong_Ai_Log.xlsx
+++ b/ai_logs/VoXuanLong_Ai_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NHOM_04_LAB211_TicketBooking\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F5AEEBA-AE27-45DB-8F1E-7188CC692CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F87BDA-EFC5-4576-9189-5B3D69B7A925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="258">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -747,6 +747,453 @@
   </si>
   <si>
     <t>Tôi có evidence?</t>
+  </si>
+  <si>
+    <t>"sửa cho tôi status của seat.csv coi ghế nào bị mua thì đổi thành SOLD"</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cập nhật đồng bộ trạng thái ghế trong </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>seats.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> theo trạng thái vé đã bán từ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>tickets.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>AI quét tickets.csv, thấy vé có status SOLD liền chuyển trạng thái tương ứng của ghế trong seats.csv thành SOLD (dẫn đến 19,411 ghế bị đổi thành SOLD).</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Nhận ra AI bị lỗi logic nghiêm trọng khi gán phẳng trạng thái. Một ghế vật lý có thể có nhiều vé cho các trận đấu (Match) khác nhau (ví dụ: Trận M1 chưa bán nhưng M2 đã bán).
+Contextualization: Bài toán quản lý bán vé sân vận động yêu cầu trạng thái ghế vật lý phải dựa trên từng trận đấu hoặc trạng thái đặt thực tế theo luồng ứng dụng (bookSeat), không thể ghi đè toàn bộ seats.csv.
+Creative Synthesis: Đề xuất reset toàn bộ 20,000 ghế về AVAILABLE và chỉ cập nhật SOLD khi fan thực hiện transaction đặt vé trực tiếp.
+Decision: Hủy bỏ script update hàng loạt của AI, yêu cầu AI viết script reset lại file seats.csv về trạng thái ban đầu (AVAILABLE).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Log console kết quả thống kê (19,411 SOLD vs 49,722 AVAILABLE tickets) + Diff file </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>seats.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Xử lý luồng xác nhận giao dịch đang chờ (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>PENDING -&gt; SUCCESS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) ở phía Staff/Admin.</t>
+    </r>
+  </si>
+  <si>
+    <t>Vấn đề là cách dùng, không phải lỗi code... Nhap Transaction ID de xac nhan: TR100007"</t>
+  </si>
+  <si>
+    <t>AI ban đầu thiết kế hệ thống bắt nhập Ticket ID để tìm trong ticketRepo, gây ra lỗi không tìm thấy vé vì giao dịch PENDING chưa tạo vé official.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Phát hiện AI thiết kế sai luồng nghiệp vụ (Workflow breakdown). Giao dịch chưa được Staff duyệt thì Ticket chưa thể xuất hiện trong cơ sở dữ liệu tickets.csv.
+Contextualization: Trong nghiệp vụ Ticket Booking của đồ án LAB211, PENDING transaction lưu ở danh sách chờ, việc tra cứu phải thông qua Transaction ID (TR100007) thay vì Ticket ID (T100006).
+Creative Synthesis: Hướng dẫn lại AI tái cấu trúc Menu Staff: Hiển thị danh sách PENDING Transaction -&gt; Nhập Transaction ID -&gt; Gọi staffConfirmTransaction -&gt; Lưu trạng thái SUCCESS.
+Decision: Yêu cầu AI sửa lại hàm adminManageBookings theo đúng các bước truy vết theo Transaction ID.</t>
+  </si>
+  <si>
+    <t>Terminal output lỗi không tìm thấy Ticket ID và màn hình menu Staff sau khi fix thành công</t>
+  </si>
+  <si>
+    <t>Thiết kế quy tắc kiểm tra tính hợp lệ (Validation) cho đầu vào giá vé VIP/NORMAL khi Admin cập nhật.</t>
+  </si>
+  <si>
+    <t>"giá mới nhập bao nhiêu là hợp lệ"</t>
+  </si>
+  <si>
+    <t>AI trả lời giá hợp lệ chỉ cần là số và $&gt; 0$, chấp nhận cả số thập phân như 1500000.5.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Nhận ra AI đang đơn giản hóa quy tắc (Oversimplification). Giá vé sự kiện bằng VNĐ không dùng số thập phân và cần có giới hạn khoảng giá hợp lý (Min/Max).Contextualization: Trong ứng dụng Java Console, việc cho phép nhập số thực lẻ sẽ làm phức tạp hoá tính toán tiền tệ và không sát với thực tế mệnh giá tiền Việt Nam.Creative Synthesis: Đề xuất mô hình hóa lại điều kiện Validation: Ràng buộc kiểu dữ liệu số nguyên, kiểm tra điều kiện $&gt; 0$ và đề xuất bổ sung biên giá trị tối thiểu/tối đa cho từng loại vé.Decision: Tiếp tục sử dụng hàm ép kiểu số hiện tại để pass các test-case cơ bản, đồng thời ghi nhận điều kiện biên giá để hoàn thiện ở bước Refactor.</t>
+  </si>
+  <si>
+    <t>Đoạn chat tư vấn của AI và đoạn code kiểm tra try-catch ép kiểu số trong Controller.</t>
+  </si>
+  <si>
+    <t>Xử lý sự bất đồng bộ giữa dữ liệu mẫu tạo sẵn (tickets.csv chứa 100,010 bản ghi) và tập dữ liệu danh sách ghế (seats.csv chứa 20,000 ghế).</t>
+  </si>
+  <si>
+    <t>"tổng seat từ ticket trước là còn bao avaliable... thì chỉnh lại seatcsv giống đi"</t>
+  </si>
+  <si>
+    <t>AI phân tích tập dữ liệu tickets.csv và giải thích nguyên nhân không thể cross-reference 1:1, sau đó thực hiện script reset toàn bộ 20,000 ghế về trạng thái AVAILABLE.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Nhận diện mẫu dữ liệu (Pattern Recognition): Nhận ra quan hệ giữa Seat và Ticket là quan hệ $1 - N$ (1 ghế vật lý xuất hiện ở $N$ trận đấu khác nhau). Việc cố ép dữ liệu từ tickets.csv sang seats.csv sẽ gây ra lỗi toàn vẹn dữ liệu (Data Inconsistency).Contextualization: Trong thiết kế cơ sở dữ liệu file CSV của đồ án, file seats.csv chỉ đóng vai trò lưu cấu hình sơ đồ ghế gốc của tĩnh vật lý, còn trạng thái vé bán ra phải được quản lý theo từng trận đấu cụ thể (MatchID).Creative Synthesis: Đề xuất tách biệt hoàn toàn vai trò của 2 file: seats.csv giữ nguyên trạng thái khởi tạo AVAILABLE làm Master Data, mọi thao tác đặt vé / đổi trạng thái sẽ do Controller quản lý runtime khi người dùng thực hiện giao dịch.Decision: Thống nhất reset toàn bộ 20,000 dòng trong seats.csv về AVAILABLE và ngắt cơ chế tự động đồng bộ ngược từ tickets.csv</t>
+  </si>
+  <si>
+    <t>Con số thống kê 100,010 dòng trong tickets.csv (49,722 AVAILABLE, 50,285 SOLD, 3 CANCELLED) và log xác nhận reset thành công 20,000 ghế trong seats.csv.</t>
+  </si>
+  <si>
+    <t>AI khẳng định có thể đồng bộ trạng thái SOLD cho seats.csv bằng cách kiểm tra các vé có status SOLD trong tickets.csv.</t>
+  </si>
+  <si>
+    <r>
+      <t>Một ghế vật lý (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>SEAT2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) có nhiều vé tương ứng với các trận đấu khác nhau (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>M1, M2...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">). Vé </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>SOLD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ở trận này không đồng nghĩa với việc ghế đó đã bán ở tất cả các trận khác.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tôi kiểm tra kết quả sau khi AI chạy script: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>19,411</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ghế bị chuyển sang </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>SOLD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> một cách vô lý, trong khi tổng số vé khả dụng (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>AVAILABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) trong </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>tickets.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vẫn còn tới </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>49,722</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vé.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bác bỏ phương án cập nhật phẳng hàng loạt của AI, yêu cầu AI viết script reset lại toàn bộ 20,000 ghế về </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>AVAILABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để quản lý đúng luồng giao dịch.</t>
+    </r>
+  </si>
+  <si>
+    <t>AI thiết kế luồng xác nhận giao dịch PENDING bằng cách yêu cầu nhập Ticket ID và cho hệ thống tra cứu trong ticketRepo.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Đối với giao dịch đang ở trạng thái </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>PENDING</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, vé chưa được thanh toán thành công nên chưa được khởi tạo và chưa tồn tại trong kho </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ticketRepo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thử nghiệm thực tế trên Terminal khi nhập mã </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>TR100007</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> thì hệ thống báo không tìm thấy vé trong dữ liệu.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tôi chất vấn lại AI, chỉ rõ điểm sai logic và yêu cầu sửa lại luồng: hiển thị danh sách PENDING transactions và cho tra cứu theo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Transaction ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI khẳng định giá vé mới nhập chỉ cần là kiểu số và lớn hơn 0 ($&gt;0$), chấp nhận cả số thập phân như </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>1500000.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Trong thực tế nghiệp vụ bán vé sự kiện bằng VNĐ, giá vé không dùng số thập phân và cần có khoảng giới hạn hợp lý (Min/Max) để tránh nhập sai dữ liệu.</t>
+  </si>
+  <si>
+    <t>Rà soát lại logic kiểm tra đầu vào trong câu trả lời tư vấn của AI và phát hiện AI không đặt bất kỳ ràng buộc thực tế nào cho các loại vé VIP/NORMAL.</t>
+  </si>
+  <si>
+    <t>Nhận diện đây là điểm AI đang đơn giản hóa quá mức, chủ động ghi nhận để bổ sung các quy tắc kiểm tra kiểu dữ liệu số nguyên và khoảng giá trị ở bước refactor.</t>
   </si>
 </sst>
 </file>
@@ -756,7 +1203,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -859,6 +1306,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -913,7 +1379,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -983,12 +1449,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -998,6 +1464,13 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1302,7 +1775,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
@@ -1311,8 +1784,8 @@
     <col min="5" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="30"/>
@@ -1321,12 +1794,12 @@
       <c r="E1" s="30"/>
       <c r="F1" s="30"/>
     </row>
-    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="18">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="14.4">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1334,7 +1807,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="14.4">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1342,7 +1815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="14.4">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -1350,7 +1823,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="14.4">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -1358,40 +1831,40 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="18">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="14.4">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C10">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="14.4">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="3">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="14.4">
       <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="4">
         <f>C11/C10</f>
-        <v>0.18571428571428572</v>
+        <v>0.14655172413793102</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="14.4">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
@@ -1399,12 +1872,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="18">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="14.4">
       <c r="A16" s="6" t="s">
         <v>17</v>
       </c>
@@ -1418,7 +1891,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4">
       <c r="A17" s="7" t="s">
         <v>21</v>
       </c>
@@ -1432,7 +1905,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4">
       <c r="A18" s="7" t="s">
         <v>25</v>
       </c>
@@ -1446,7 +1919,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4">
       <c r="A19" s="7" t="s">
         <v>29</v>
       </c>
@@ -1460,7 +1933,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4">
       <c r="A20" s="7" t="s">
         <v>32</v>
       </c>
@@ -1468,12 +1941,12 @@
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
     </row>
-    <row r="22" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" ht="18">
       <c r="A22" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="14.4">
       <c r="A23" s="6" t="s">
         <v>34</v>
       </c>
@@ -1484,45 +1957,45 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4">
       <c r="A24" s="7" t="s">
         <v>37</v>
       </c>
       <c r="B24" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4">
       <c r="A25" s="7" t="s">
         <v>39</v>
       </c>
       <c r="B25" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4">
       <c r="A26" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B26" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4">
       <c r="A27" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B27" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>38</v>
@@ -1539,7 +2012,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="18" customWidth="1"/>
@@ -1550,8 +2023,8 @@
     <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="29" t="s">
         <v>42</v>
       </c>
       <c r="B1" s="30"/>
@@ -1562,8 +2035,8 @@
       <c r="G1" s="30"/>
       <c r="H1" s="30"/>
     </row>
-    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+    <row r="2" spans="1:8" ht="30" customHeight="1">
+      <c r="A2" s="31" t="s">
         <v>43</v>
       </c>
       <c r="B2" s="30"/>
@@ -1574,7 +2047,7 @@
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
     </row>
-    <row r="3" spans="1:8" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="39.9" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>44</v>
       </c>
@@ -1600,7 +2073,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="99.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="99.9" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>52</v>
       </c>
@@ -1626,7 +2099,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="99.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="99.9" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>59</v>
       </c>
@@ -1652,7 +2125,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="99.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="99.9" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>66</v>
       </c>
@@ -1678,7 +2151,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A7" s="7">
         <v>4</v>
       </c>
@@ -1704,7 +2177,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A8" s="7">
         <v>5</v>
       </c>
@@ -1730,7 +2203,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A9" s="7">
         <v>6</v>
       </c>
@@ -1756,7 +2229,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A10" s="7">
         <v>7</v>
       </c>
@@ -1782,7 +2255,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A11" s="7">
         <v>8</v>
       </c>
@@ -1808,7 +2281,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A12" s="7">
         <v>9</v>
       </c>
@@ -1834,7 +2307,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A13" s="7">
         <v>10</v>
       </c>
@@ -1860,7 +2333,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A14" s="7">
         <v>11</v>
       </c>
@@ -1886,7 +2359,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A15" s="7">
         <v>12</v>
       </c>
@@ -1912,7 +2385,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A16" s="7">
         <v>13</v>
       </c>
@@ -1938,7 +2411,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A17" s="7">
         <v>14</v>
       </c>
@@ -1964,7 +2437,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A18" s="7">
         <v>15</v>
       </c>
@@ -1990,7 +2463,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A19" s="7">
         <v>16</v>
       </c>
@@ -2012,78 +2485,141 @@
       <c r="G19" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="H19" s="28" t="s">
+      <c r="H19" s="21" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-    </row>
-    <row r="21" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-    </row>
-    <row r="22" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-    </row>
-    <row r="23" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-    </row>
-    <row r="24" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="80.099999999999994" customHeight="1">
+      <c r="A20" s="7">
+        <v>17</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="G20" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="80.099999999999994" customHeight="1">
+      <c r="A21" s="7">
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="80.099999999999994" customHeight="1">
+      <c r="A22" s="7">
+        <v>19</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="80.099999999999994" customHeight="1">
+      <c r="A23" s="7">
+        <v>20</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
+      <c r="G24" s="37"/>
       <c r="H24" s="7"/>
     </row>
-    <row r="25" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
       <c r="H25" s="7"/>
     </row>
-    <row r="26" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
+      <c r="G26" s="35"/>
       <c r="H26" s="7"/>
     </row>
   </sheetData>
@@ -2098,14 +2634,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="33" t="s">
         <v>138</v>
       </c>
@@ -2115,7 +2651,7 @@
       <c r="E1" s="30"/>
       <c r="F1" s="30"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="32" t="s">
         <v>139</v>
       </c>
@@ -2125,7 +2661,7 @@
       <c r="E2" s="30"/>
       <c r="F2" s="30"/>
     </row>
-    <row r="3" spans="1:6" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="39.9" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>140</v>
       </c>
@@ -2145,7 +2681,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="60" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>66</v>
       </c>
@@ -2165,7 +2701,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="82.8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="82.8">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -2185,7 +2721,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="60" customHeight="1">
       <c r="A6" s="7">
         <v>8</v>
       </c>
@@ -2205,7 +2741,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="60" customHeight="1">
       <c r="A7" s="7">
         <v>10</v>
       </c>
@@ -2225,7 +2761,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="60" customHeight="1">
       <c r="A8" s="7">
         <v>11</v>
       </c>
@@ -2245,7 +2781,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="60" customHeight="1">
       <c r="A9" s="7">
         <v>13</v>
       </c>
@@ -2265,7 +2801,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="60" customHeight="1">
       <c r="A10" s="7">
         <v>16</v>
       </c>
@@ -2285,31 +2821,67 @@
         <v>176</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-    </row>
-    <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-    </row>
-    <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="60" customHeight="1">
+      <c r="A11" s="7">
+        <v>17</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="60" customHeight="1">
+      <c r="A12" s="7">
+        <v>18</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="60" customHeight="1">
+      <c r="A13" s="7">
+        <v>19</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="60" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -2317,7 +2889,7 @@
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="60" customHeight="1">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -2325,7 +2897,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="60" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -2333,7 +2905,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
     </row>
-    <row r="17" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="60" customHeight="1">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -2341,7 +2913,7 @@
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="60" customHeight="1">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -2349,7 +2921,7 @@
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="60" customHeight="1">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -2357,7 +2929,7 @@
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="60" customHeight="1">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -2365,7 +2937,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="60" customHeight="1">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -2373,7 +2945,7 @@
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="60" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -2381,7 +2953,7 @@
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="60" customHeight="1">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -2389,7 +2961,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="60" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -2397,12 +2969,12 @@
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
     </row>
-    <row r="30" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="18">
       <c r="A30" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="14.4">
       <c r="A31" s="10" t="s">
         <v>178</v>
       </c>
@@ -2413,7 +2985,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="27.6">
       <c r="A32" s="7" t="s">
         <v>146</v>
       </c>
@@ -2424,7 +2996,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="27.6">
       <c r="A33" s="7" t="s">
         <v>156</v>
       </c>
@@ -2435,7 +3007,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="27.6">
       <c r="A34" s="7" t="s">
         <v>151</v>
       </c>
@@ -2446,7 +3018,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="27.6">
       <c r="A35" s="7" t="s">
         <v>187</v>
       </c>
@@ -2457,7 +3029,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="41.4">
       <c r="A36" s="7" t="s">
         <v>190</v>
       </c>
@@ -2480,7 +3052,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
@@ -2488,15 +3060,15 @@
     <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="29" t="s">
         <v>193</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
       <c r="D1" s="30"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" s="34" t="s">
         <v>194</v>
       </c>
@@ -2504,12 +3076,12 @@
       <c r="C2" s="30"/>
       <c r="D2" s="30"/>
     </row>
-    <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="18">
       <c r="A4" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="14.4">
       <c r="A5" s="6" t="s">
         <v>196</v>
       </c>
@@ -2523,7 +3095,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" s="12" t="s">
         <v>200</v>
       </c>
@@ -2535,7 +3107,7 @@
       </c>
       <c r="D6" s="13"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" s="12" t="s">
         <v>203</v>
       </c>
@@ -2547,7 +3119,7 @@
       </c>
       <c r="D7" s="13"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" s="12" t="s">
         <v>205</v>
       </c>
@@ -2559,7 +3131,7 @@
       </c>
       <c r="D8" s="13"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" s="12" t="s">
         <v>207</v>
       </c>
@@ -2571,7 +3143,7 @@
       </c>
       <c r="D9" s="13"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
         <v>209</v>
       </c>
@@ -2583,12 +3155,12 @@
       </c>
       <c r="D10" s="13"/>
     </row>
-    <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="18">
       <c r="A12" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="14.4">
       <c r="A13" s="6" t="s">
         <v>196</v>
       </c>
@@ -2602,7 +3174,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" s="12" t="s">
         <v>200</v>
       </c>
@@ -2614,7 +3186,7 @@
       </c>
       <c r="D14" s="13"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">
         <v>203</v>
       </c>
@@ -2626,7 +3198,7 @@
       </c>
       <c r="D15" s="13"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16" s="12" t="s">
         <v>205</v>
       </c>
@@ -2638,7 +3210,7 @@
       </c>
       <c r="D16" s="13"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4">
       <c r="A17" s="12" t="s">
         <v>207</v>
       </c>
@@ -2650,7 +3222,7 @@
       </c>
       <c r="D17" s="13"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4">
       <c r="A18" s="12" t="s">
         <v>209</v>
       </c>
@@ -2662,32 +3234,32 @@
       </c>
       <c r="D18" s="13"/>
     </row>
-    <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="15.6">
       <c r="A20" s="14" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="14.4">
       <c r="A21" s="15" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="14.4">
       <c r="A22" s="15" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" ht="18">
       <c r="A25" s="1" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="14.4">
       <c r="A26" s="16" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="43.2">
       <c r="A27" s="17" t="s">
         <v>44</v>
       </c>
@@ -2701,7 +3273,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4">
       <c r="A28" s="9" t="s">
         <v>52</v>
       </c>
@@ -2709,7 +3281,7 @@
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4">
       <c r="A29" s="9" t="s">
         <v>59</v>
       </c>
@@ -2717,7 +3289,7 @@
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4">
       <c r="A30" s="9" t="s">
         <v>66</v>
       </c>

--- a/ai_logs/VoXuanLong_Ai_Log.xlsx
+++ b/ai_logs/VoXuanLong_Ai_Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NHOM_04_LAB211_TicketBooking\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F87BDA-EFC5-4576-9189-5B3D69B7A925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{824FFF08-E1AB-4714-9E4C-DA619BF4D16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6240" yWindow="264" windowWidth="16800" windowHeight="13056" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="281">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -1194,6 +1194,385 @@
   </si>
   <si>
     <t>Nhận diện đây là điểm AI đang đơn giản hóa quá mức, chủ động ghi nhận để bổ sung các quy tắc kiểm tra kiểu dữ liệu số nguyên và khoảng giá trị ở bước refactor.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cần thiết kế test case mô phỏng đặt vé đồng thời để kiểm tra cơ chế đồng bộ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>synchronized</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và chứng minh không xảy ra lỗi Double Booking</t>
+    </r>
+  </si>
+  <si>
+    <t>"viết cho tôi cái test case và chạy chứng minh không double booking"</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI cung cấp đoạn code test Java </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>SyncBookingTest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sử dụng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ExecutorService</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (5 threads) và lớp </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>BookingRepository</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> có phương thức </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>synchronized bookTicket()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Critical Thinking: Nhận thấy test case mẫu của AI chạy 5 threads nhưng cần hiểu rõ cơ chế khóa thread để đảm bảo khi số lượt đặt vượt capacity thì các thread sau phải bị chặn.
+Contextualization: Trong môn học / dự án nhóm, việc kiểm thử đồng bộ yêu cầu minh chứng rõ ràng việc từ chối đặt vé khi hết chỗ.
+Decision: Giữ nguyên cấu trúc code SyncBookingTest, cho chạy 5 threads với capacity = 3 để xác nhận số vé thành công không bao giờ vượt quá 3.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">File code </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>SyncBookingTest.java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; Log Terminal in ra kết quả "Tổng số vé đặt thành công: 3".</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Xác định vị trí lưu trữ hợp lý cho các file class kiểm thử (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>SyncBookingTest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>SimulatorTest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) trong cấu trúc dự án Maven chuẩn.</t>
+    </r>
+  </si>
+  <si>
+    <t>"h tạo 2 cái test kia ở chỗ nào / tạo dô file nào"</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI hướng dẫn tạo file test nằm trong thư mục </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>src/test/java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (cụ thể là package </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ticket</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) để tuân thủ quy tắc tổ chức dự án Maven.</t>
+    </r>
+  </si>
+  <si>
+    <t>Critical Thinking: Nhận thấy nếu tạo file test trong src/main/java sẽ làm bẩn mã nguồn chính của ứng dụng và không tuân thủ chuẩn Maven.
+Contextualization: Dự án nhóm đã phân chia các package ticket, core, seat rõ ràng trong src/test/java.
+Decision: Tạo file SyncBookingTest.java trực tiếp bên trong thư mục src/test/java/ticket để quản lý test case độc lập.</t>
+  </si>
+  <si>
+    <t>Cần thử nghiệm các kịch bản đặt vé với các quy mô tải và số lượng ghế trống khác nhau để kiểm tra độ bền của cơ chế đồng bộ.</t>
+  </si>
+  <si>
+    <t>"có thể sửa số người đặt không / có thể sửa capacity không"</t>
+  </si>
+  <si>
+    <t>Thư mục src/test/java/ticket trên VS Code Explorer chứa file test.011PROBLEM-SOLVINGPattern RecognitionCần thử nghiệm các kịch bản đặt vé với các quy mô tải và số lượng ghế trống khác nhau để kiểm tra độ bền của cơ chế đồng bộ."có thể sửa số người đặt không / có thể sửa capacity không"AI hướng dẫn cách điều chỉnh thông số THREAD_COUNT (số vòng lặp for tạo thread) và số ghế tối đa capacity trong constructor của BookingRepository.Critical Thinking: Kiểm thử với 5 threads chưa phản ánh hết các tình huống tranh chấp tài nguyên (race condition) phức tạp hơn.Contextualization: Cần thử nghiệm thay đổi linh hoạt giữa các con số (vd: 10/20 threads với capacity 3/10) để quan sát log lỗi từ chối.Decision: Sửa tham số truyền vào để chạy thử nhiều kịch bản, xác nhận hệ thống luôn chặn chính xác khi số người dùng vượt quá capacity.Sửa tham số trong SyncBookingTest.java và xem kết quả tương ứng trên Console.012VERIFICATIONAbstractionCần làm rõ bản chất của Thread trong Java và lý do phải dùng đa luồng để test đồng bộ thay vì chạy vòng lặp tuần tự."cái thread là sao"AI giải thích khái niệm Thread trong Java là luồng thực thi song song, giúp mô phỏng nhiều người dùng đồng thời truy cập vào hệ thống tại cùng một thời điểm.Critical Thinking: Nhận ra nếu chỉ dùng vòng lặp for thông thường (đơn luồng), các giao dịch sẽ chạy tuần tự nên không thể phát hiện lỗi tranh chấp dữ liệu (Race Condition).Contextualization: Bài toán đặt vé bóng đá yêu cầu xử lý hàng trăm người bấm đặt vé cùng 1 giây.Decision: Tiếp tục sử dụng ExecutorService và CountDownLatch để tạo các luồng chạy song song thật sự khi test.Đoạn code khởi tạo Executors.newFixedThreadPool() trong file test.013VERIFICATIONAbstractionPhân biệt môi trường và cách thức vận hành giữa việc chạy Test độc lập (Run/Debug) và chạy qua Menu chính của ứng dụng (Main.java)."dẫy là nó test bên ngoài đúng không / test bên ngoài là test trên run hoặc debug hả"AI xác nhận test case ở Tuần 7–8 là unit/integration test chạy độc lập bằng lệnh Run/Debug trực tiếp trên file test mà không qua giao diện Menu chính.Critical Thinking: Phân định rõ ranh giới giữa kiểm thử logic cốt lõi (Core Logic) và kiểm thử giao diện người dùng (UI/Menu).Contextualization: Yêu cầu Tuần 7–8 tập trung chứng minh thuật toán và hiệu năng đồng bộ, chưa cần tích hợp vào Menu chính.Decision: Chạy trực tiếp file SyncBookingTest.java và SimulatorTest.java qua tính năng Run Java trên VS Code để tập trung lấy log kết quả.Thao tác Run Java trên VS Code và màn hình Console Terminal độc lập.014PROBLEM-SOLVINGAlgorithmsChạy mô phỏng tải lớn (Week 8) với hàng trăm threads đồng thời, kiểm tra việc phát hiện trùng ghế và xuất báo cáo Simulation."chạy cái tuần 8 dầy đúng chưa"AI phân tích log console (các dòng [ERROR] Seat SEAT... is already booked), xác nhận hệ thống đã bắt lỗi trùng ghế chính xác và chạy xong tuần 8.Critical Thinking: Kiểm tra đối soát bảng Simulation Summary Report thu được từ terminal để đảm bảo không có giao dịch trùng lặp nào bị lọt lưới.Contextualization: Dữ liệu mô phỏng từ các lượt chạy này sẽ được ghi nhận lại để làm đầu vào cho báo cáo phân tích ở Tuần 9.Decision: Chấp nhận kết quả mô phỏng, xuất dữ liệu ra file log/CSV để chuẩn bị cho giai đoạn đánh giá hiệu năng tiếp theo.Màn hình Terminal in báo cáo Simulation Summary Report và các log lỗi trùng ghế [ERROR].</t>
+  </si>
+  <si>
+    <t>AI hướng dẫn cách điều chỉnh thông số THREAD_COUNT (số vòng lặp for tạo thread) và số ghế tối đa capacity trong constructor của BookingRepository.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Kiểm thử với 5 threads chưa phản ánh hết các tình huống tranh chấp tài nguyên (race condition) phức tạp hơn.
+Contextualization: Cần thử nghiệm thay đổi linh hoạt giữa các con số (vd: 10/20 threads với capacity 3/10) để quan sát log lỗi từ chối.
+Decision: Sửa tham số truyền vào để chạy thử nhiều kịch bản, xác nhận hệ thống luôn chặn chính xác khi số người dùng vượt quá capacity.</t>
+  </si>
+  <si>
+    <t>Sửa tham số trong SyncBookingTest.java và xem kết quả tương ứng trên Console.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI đề xuất chỉ cần khởi tạo danh sách ghế và gọi trực tiếp hàm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>bookTicket()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tuần tự trong vòng lặp </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>for</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để test chức năng đặt vé.</t>
+    </r>
+  </si>
+  <si>
+    <t>Trong thực tế hệ thống bán vé bóng đá có hàng ngàn người bấm đặt vé cùng lúc, việc chạy vòng lặp đơn luồng tuần tự không thể phát hiện lỗi tranh chấp dữ liệu (Race Condition) và lỗi đặt trùng ghế (Double Booking).</t>
+  </si>
+  <si>
+    <t>Tôi rà soát lại phương pháp test và nhận thấy chạy đơn luồng sẽ luôn trả về thành công 100%, không phản ánh đúng môi trường vận hành đa luồng thực tế.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bác bỏ gợi ý test đơn luồng của AI, chủ động chuyển sang sử dụng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ExecutorService</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (đa luồng) và </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>CountDownLatch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để ép các thread truy cập song song đồng thời.</t>
+    </r>
+  </si>
+  <si>
+    <t>AI cho rằng chỉ cần test cố định 1 kịch bản với 5 người dùng và 3 ghế trống là đủ để chứng minh cơ chế đồng bộ hoạt động chính xác 100% trong mọi trường hợp.</t>
+  </si>
+  <si>
+    <t>Một kịch bản tải nhỏ (5 threads) không đủ độ bao phủ để phát hiện các lỗi nghẽn cổ đống (bottleneck), đan xen luồng (thread interleaving) hoặc vượt tải dung lượng lớn.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tôi thay đổi linh hoạt các tham số </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>capacity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>THREAD_COUNT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> lên các quy mô khác nhau (10, 20, 100, 500 threads) để đối soát kết quả console.</t>
+    </r>
+  </si>
+  <si>
+    <t>Chất vấn AI và chủ động chỉnh sửa mã nguồn test case để hỗ trợ thay đổi tham số đầu vào linh hoạt, chạy thử nhiều quy mô tải trước khi kết luận.</t>
   </si>
 </sst>
 </file>
@@ -1203,7 +1582,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1307,14 +1686,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
@@ -1379,7 +1750,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1465,12 +1836,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1841,7 +2211,7 @@
         <v>11</v>
       </c>
       <c r="C10">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.4">
@@ -1849,7 +2219,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="14.4">
@@ -1858,7 +2228,7 @@
       </c>
       <c r="C12" s="4">
         <f>C11/C10</f>
-        <v>0.14655172413793102</v>
+        <v>0.15873015873015872</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>14</v>
@@ -1869,7 +2239,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18">
@@ -1962,7 +2332,7 @@
         <v>37</v>
       </c>
       <c r="B24" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>38</v>
@@ -1973,7 +2343,7 @@
         <v>39</v>
       </c>
       <c r="B25" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>38</v>
@@ -1995,7 +2365,7 @@
         <v>41</v>
       </c>
       <c r="B27" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>38</v>
@@ -2011,7 +2381,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2411,7 +2781,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="17" spans="1:11" ht="80.099999999999994" customHeight="1">
       <c r="A17" s="7">
         <v>14</v>
       </c>
@@ -2437,7 +2807,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="18" spans="1:11" ht="80.099999999999994" customHeight="1">
       <c r="A18" s="7">
         <v>15</v>
       </c>
@@ -2463,7 +2833,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="19" spans="1:11" ht="80.099999999999994" customHeight="1">
       <c r="A19" s="7">
         <v>16</v>
       </c>
@@ -2489,7 +2859,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="20" spans="1:11" ht="80.099999999999994" customHeight="1">
       <c r="A20" s="7">
         <v>17</v>
       </c>
@@ -2508,14 +2878,14 @@
       <c r="F20" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="G20" s="36" t="s">
+      <c r="G20" s="21" t="s">
         <v>229</v>
       </c>
       <c r="H20" s="21" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="21" spans="1:11" ht="80.099999999999994" customHeight="1">
       <c r="A21" s="7">
         <v>18</v>
       </c>
@@ -2541,7 +2911,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="22" spans="1:11" ht="80.099999999999994" customHeight="1">
       <c r="A22" s="7">
         <v>19</v>
       </c>
@@ -2567,7 +2937,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="80.099999999999994" customHeight="1">
+    <row r="23" spans="1:11" ht="80.099999999999994" customHeight="1">
       <c r="A23" s="7">
         <v>20</v>
       </c>
@@ -2593,34 +2963,86 @@
         <v>245</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="7"/>
-    </row>
-    <row r="25" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="H25" s="7"/>
-    </row>
-    <row r="26" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="7"/>
+    <row r="24" spans="1:11" ht="80.099999999999994" customHeight="1">
+      <c r="A24" s="7">
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="G24" s="36" t="s">
+        <v>261</v>
+      </c>
+      <c r="H24" s="28" t="s">
+        <v>262</v>
+      </c>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+    </row>
+    <row r="25" spans="1:11" ht="80.099999999999994" customHeight="1">
+      <c r="A25" s="7">
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="80.099999999999994" customHeight="1">
+      <c r="A26" s="7">
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="G26" s="35" t="s">
+        <v>271</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>272</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2882,24 +3304,48 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="60" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="A14" s="7">
+        <v>21</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>275</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="15" spans="1:6" ht="60" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="A15" s="7">
+        <v>22</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="16" spans="1:6" ht="60" customHeight="1">
       <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
+      <c r="B16" s="26"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
